--- a/data/nzd0097/nzd0097.xlsx
+++ b/data/nzd0097/nzd0097.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE264"/>
+  <dimension ref="A1:AE265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26560,6 +26560,105 @@
       <c r="AE264" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>392.88</v>
+      </c>
+      <c r="C265" t="n">
+        <v>397.45</v>
+      </c>
+      <c r="D265" t="n">
+        <v>378.78</v>
+      </c>
+      <c r="E265" t="n">
+        <v>364.73</v>
+      </c>
+      <c r="F265" t="n">
+        <v>360.08</v>
+      </c>
+      <c r="G265" t="n">
+        <v>360.48</v>
+      </c>
+      <c r="H265" t="n">
+        <v>363.37</v>
+      </c>
+      <c r="I265" t="n">
+        <v>373.28</v>
+      </c>
+      <c r="J265" t="n">
+        <v>375.97</v>
+      </c>
+      <c r="K265" t="n">
+        <v>381.42</v>
+      </c>
+      <c r="L265" t="n">
+        <v>388.38</v>
+      </c>
+      <c r="M265" t="n">
+        <v>391.54</v>
+      </c>
+      <c r="N265" t="n">
+        <v>391.97</v>
+      </c>
+      <c r="O265" t="n">
+        <v>388.87</v>
+      </c>
+      <c r="P265" t="n">
+        <v>390.91</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>393.38</v>
+      </c>
+      <c r="R265" t="n">
+        <v>388.98</v>
+      </c>
+      <c r="S265" t="n">
+        <v>387.57</v>
+      </c>
+      <c r="T265" t="n">
+        <v>382.81</v>
+      </c>
+      <c r="U265" t="n">
+        <v>379.73</v>
+      </c>
+      <c r="V265" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="W265" t="n">
+        <v>377.91</v>
+      </c>
+      <c r="X265" t="n">
+        <v>383.3</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>382.77</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>373.44</v>
+      </c>
+      <c r="AA265" t="n">
+        <v>371.52</v>
+      </c>
+      <c r="AB265" t="n">
+        <v>381.98</v>
+      </c>
+      <c r="AC265" t="n">
+        <v>397.05</v>
+      </c>
+      <c r="AD265" t="n">
+        <v>395.77</v>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26574,7 +26673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B266"/>
+  <dimension ref="A1:B267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29237,6 +29336,16 @@
       </c>
       <c r="B266" t="n">
         <v>-0.37</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>
@@ -29405,28 +29514,28 @@
         <v>0.0566</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07250953096061498</v>
+        <v>0.07295888682564766</v>
       </c>
       <c r="J2" t="n">
+        <v>264</v>
+      </c>
+      <c r="K2" t="n">
         <v>263</v>
       </c>
-      <c r="K2" t="n">
-        <v>262</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.006816163578278522</v>
+        <v>0.006957494869637926</v>
       </c>
       <c r="M2" t="n">
-        <v>4.426828395682503</v>
+        <v>4.41218563534273</v>
       </c>
       <c r="N2" t="n">
-        <v>38.99524271152291</v>
+        <v>38.84820456673114</v>
       </c>
       <c r="O2" t="n">
-        <v>6.244617098871869</v>
+        <v>6.232832788285848</v>
       </c>
       <c r="P2" t="n">
-        <v>390.4013407415815</v>
+        <v>390.3964484125538</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -29487,28 +29596,28 @@
         <v>0.0609</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02415763597417946</v>
+        <v>-0.02635643911265747</v>
       </c>
       <c r="J3" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K3" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009536447278877258</v>
+        <v>0.001143338170628838</v>
       </c>
       <c r="M3" t="n">
-        <v>4.432349924047355</v>
+        <v>4.42538732105618</v>
       </c>
       <c r="N3" t="n">
-        <v>31.07155504427063</v>
+        <v>30.9824533473105</v>
       </c>
       <c r="O3" t="n">
-        <v>5.574186491701783</v>
+        <v>5.566188403864039</v>
       </c>
       <c r="P3" t="n">
-        <v>400.8844833092064</v>
+        <v>400.9084778707686</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29565,28 +29674,28 @@
         <v>0.132</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006523950784670299</v>
+        <v>0.00333957442832328</v>
       </c>
       <c r="J4" t="n">
+        <v>264</v>
+      </c>
+      <c r="K4" t="n">
         <v>263</v>
       </c>
-      <c r="K4" t="n">
-        <v>262</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0001158774225549219</v>
+        <v>3.051954565769233e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.379475547977101</v>
+        <v>3.383171424224682</v>
       </c>
       <c r="N4" t="n">
-        <v>18.69156364613601</v>
+        <v>18.68238817646026</v>
       </c>
       <c r="O4" t="n">
-        <v>4.323374104346745</v>
+        <v>4.322312827232691</v>
       </c>
       <c r="P4" t="n">
-        <v>382.6691952822539</v>
+        <v>382.7038677119104</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29643,28 +29752,28 @@
         <v>0.1347</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09267735972086744</v>
+        <v>0.09084650474786883</v>
       </c>
       <c r="J5" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K5" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02018973085942111</v>
+        <v>0.01955625233898117</v>
       </c>
       <c r="M5" t="n">
-        <v>3.549242774970119</v>
+        <v>3.544933429182691</v>
       </c>
       <c r="N5" t="n">
-        <v>21.24641260838492</v>
+        <v>21.18640997332978</v>
       </c>
       <c r="O5" t="n">
-        <v>4.609383104970222</v>
+        <v>4.602869754113164</v>
       </c>
       <c r="P5" t="n">
-        <v>364.6375909982394</v>
+        <v>364.657480494509</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29721,28 +29830,28 @@
         <v>0.114</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2429429634332007</v>
+        <v>0.2383877133481395</v>
       </c>
       <c r="J6" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K6" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1081793762441752</v>
+        <v>0.1048837738352838</v>
       </c>
       <c r="M6" t="n">
-        <v>3.821355951192719</v>
+        <v>3.832071797528006</v>
       </c>
       <c r="N6" t="n">
-        <v>24.80096254383776</v>
+        <v>24.83377474829978</v>
       </c>
       <c r="O6" t="n">
-        <v>4.980056479984715</v>
+        <v>4.983349751753311</v>
       </c>
       <c r="P6" t="n">
-        <v>359.5189082867547</v>
+        <v>359.5683942541908</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29799,28 +29908,28 @@
         <v>0.1066</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2230984447253508</v>
+        <v>0.2160390675188502</v>
       </c>
       <c r="J7" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K7" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1154945291162549</v>
+        <v>0.1083824444526689</v>
       </c>
       <c r="M7" t="n">
-        <v>3.442904713976117</v>
+        <v>3.466075783016788</v>
       </c>
       <c r="N7" t="n">
-        <v>19.42938459330103</v>
+        <v>19.66020919813571</v>
       </c>
       <c r="O7" t="n">
-        <v>4.407877561060542</v>
+        <v>4.433983445857203</v>
       </c>
       <c r="P7" t="n">
-        <v>363.6398686693645</v>
+        <v>363.7165582262575</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29877,28 +29986,28 @@
         <v>0.1191</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1147844582789602</v>
+        <v>0.1069348571792099</v>
       </c>
       <c r="J8" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K8" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03368057461082019</v>
+        <v>0.0290482829414308</v>
       </c>
       <c r="M8" t="n">
-        <v>3.376839672809795</v>
+        <v>3.405943703158481</v>
       </c>
       <c r="N8" t="n">
-        <v>19.26789381397265</v>
+        <v>19.5712981417355</v>
       </c>
       <c r="O8" t="n">
-        <v>4.389520909390073</v>
+        <v>4.423945992181132</v>
       </c>
       <c r="P8" t="n">
-        <v>370.3792058760566</v>
+        <v>370.4644800316255</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29955,28 +30064,28 @@
         <v>0.1247</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1135146111786297</v>
+        <v>0.109731872965276</v>
       </c>
       <c r="J9" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K9" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03536381498462471</v>
+        <v>0.03323398828529467</v>
       </c>
       <c r="M9" t="n">
-        <v>3.225638381060618</v>
+        <v>3.231455690377089</v>
       </c>
       <c r="N9" t="n">
-        <v>17.91574282140384</v>
+        <v>17.93528873833084</v>
       </c>
       <c r="O9" t="n">
-        <v>4.232699235878193</v>
+        <v>4.235007525179954</v>
       </c>
       <c r="P9" t="n">
-        <v>375.1280128431009</v>
+        <v>375.1691066264388</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30033,28 +30142,28 @@
         <v>0.1072</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1600703533107057</v>
+        <v>0.15590339767678</v>
       </c>
       <c r="J10" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K10" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0501432057022666</v>
+        <v>0.04787381196095941</v>
       </c>
       <c r="M10" t="n">
-        <v>3.682261561796955</v>
+        <v>3.688328422422619</v>
       </c>
       <c r="N10" t="n">
-        <v>24.7397150892036</v>
+        <v>24.75207079191341</v>
       </c>
       <c r="O10" t="n">
-        <v>4.973903405696937</v>
+        <v>4.975145303598017</v>
       </c>
       <c r="P10" t="n">
-        <v>377.0909780086708</v>
+        <v>377.1362457386435</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30111,28 +30220,28 @@
         <v>0.1173</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1180467520413902</v>
+        <v>0.1164483580562831</v>
       </c>
       <c r="J11" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K11" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03444698008295766</v>
+        <v>0.0337975657297509</v>
       </c>
       <c r="M11" t="n">
-        <v>3.599985995792049</v>
+        <v>3.592934562718146</v>
       </c>
       <c r="N11" t="n">
-        <v>19.90947947859917</v>
+        <v>19.84967141454111</v>
       </c>
       <c r="O11" t="n">
-        <v>4.462003975636862</v>
+        <v>4.455297006321925</v>
       </c>
       <c r="P11" t="n">
-        <v>380.356653006198</v>
+        <v>380.3740171621104</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30189,28 +30298,28 @@
         <v>0.1139</v>
       </c>
       <c r="I12" t="n">
-        <v>0.05378919003174186</v>
+        <v>0.05644834267466214</v>
       </c>
       <c r="J12" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K12" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L12" t="n">
-        <v>0.007000521158222583</v>
+        <v>0.00775246351453851</v>
       </c>
       <c r="M12" t="n">
-        <v>3.511252843559999</v>
+        <v>3.510010540405987</v>
       </c>
       <c r="N12" t="n">
-        <v>20.91873921927052</v>
+        <v>20.88269602810083</v>
       </c>
       <c r="O12" t="n">
-        <v>4.573700823104909</v>
+        <v>4.569758858856868</v>
       </c>
       <c r="P12" t="n">
-        <v>383.5716492696675</v>
+        <v>383.5427615601811</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30267,28 +30376,28 @@
         <v>0.1126</v>
       </c>
       <c r="I13" t="n">
-        <v>0.04480624899538315</v>
+        <v>0.0469028848946361</v>
       </c>
       <c r="J13" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K13" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L13" t="n">
-        <v>0.006403082451776676</v>
+        <v>0.007058510558452191</v>
       </c>
       <c r="M13" t="n">
-        <v>3.176394807777354</v>
+        <v>3.174034501707686</v>
       </c>
       <c r="N13" t="n">
-        <v>15.87907375289964</v>
+        <v>15.8457784192124</v>
       </c>
       <c r="O13" t="n">
-        <v>3.984855549816033</v>
+        <v>3.98067562346047</v>
       </c>
       <c r="P13" t="n">
-        <v>387.6835894490713</v>
+        <v>387.6608126412347</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30345,28 +30454,28 @@
         <v>0.1163</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1205883790507671</v>
+        <v>0.1233734896908492</v>
       </c>
       <c r="J14" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K14" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03482387645666174</v>
+        <v>0.03660403788203137</v>
       </c>
       <c r="M14" t="n">
-        <v>3.558734318504434</v>
+        <v>3.557786362641101</v>
       </c>
       <c r="N14" t="n">
-        <v>20.54315863554349</v>
+        <v>20.51272705944643</v>
       </c>
       <c r="O14" t="n">
-        <v>4.532456137189139</v>
+        <v>4.529097819593481</v>
       </c>
       <c r="P14" t="n">
-        <v>385.2421551804663</v>
+        <v>385.2118991260527</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30423,28 +30532,28 @@
         <v>0.1195</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1833524098288254</v>
+        <v>0.1846046243149721</v>
       </c>
       <c r="J15" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K15" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L15" t="n">
-        <v>0.06083758503040237</v>
+        <v>0.06208330320536715</v>
       </c>
       <c r="M15" t="n">
-        <v>3.685008064825533</v>
+        <v>3.676564080015345</v>
       </c>
       <c r="N15" t="n">
-        <v>26.45262838737025</v>
+        <v>26.36200756897388</v>
       </c>
       <c r="O15" t="n">
-        <v>5.143211874633423</v>
+        <v>5.134394566935217</v>
       </c>
       <c r="P15" t="n">
-        <v>382.4524271610562</v>
+        <v>382.4388237267492</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30501,28 +30610,28 @@
         <v>0.1336</v>
       </c>
       <c r="I16" t="n">
-        <v>0.123990503030212</v>
+        <v>0.1265624278335981</v>
       </c>
       <c r="J16" t="n">
+        <v>264</v>
+      </c>
+      <c r="K16" t="n">
         <v>263</v>
       </c>
-      <c r="K16" t="n">
-        <v>262</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.04605373143367553</v>
+        <v>0.04815880088970426</v>
       </c>
       <c r="M16" t="n">
-        <v>3.236926993678915</v>
+        <v>3.238440269295152</v>
       </c>
       <c r="N16" t="n">
-        <v>16.20942953775966</v>
+        <v>16.18818052819375</v>
       </c>
       <c r="O16" t="n">
-        <v>4.026093582836801</v>
+        <v>4.023453805897833</v>
       </c>
       <c r="P16" t="n">
-        <v>384.3737034961323</v>
+        <v>384.3457018534431</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30579,28 +30688,28 @@
         <v>0.1213</v>
       </c>
       <c r="I17" t="n">
-        <v>0.07405345837975448</v>
+        <v>0.0788208889373456</v>
       </c>
       <c r="J17" t="n">
+        <v>264</v>
+      </c>
+      <c r="K17" t="n">
         <v>263</v>
       </c>
-      <c r="K17" t="n">
-        <v>262</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.01762152591592903</v>
+        <v>0.01990569144195409</v>
       </c>
       <c r="M17" t="n">
-        <v>3.221865115318319</v>
+        <v>3.234450531321882</v>
       </c>
       <c r="N17" t="n">
-        <v>15.55963666578075</v>
+        <v>15.63920645142341</v>
       </c>
       <c r="O17" t="n">
-        <v>3.944570529953895</v>
+        <v>3.954643656693155</v>
       </c>
       <c r="P17" t="n">
-        <v>385.3535548370324</v>
+        <v>385.3016456459844</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30657,28 +30766,28 @@
         <v>0.1036</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1109239893803728</v>
+        <v>0.1135523764745687</v>
       </c>
       <c r="J18" t="n">
+        <v>264</v>
+      </c>
+      <c r="K18" t="n">
         <v>263</v>
       </c>
-      <c r="K18" t="n">
-        <v>262</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.04380147119741051</v>
+        <v>0.04603562903347469</v>
       </c>
       <c r="M18" t="n">
-        <v>2.905327468074512</v>
+        <v>2.905972066984948</v>
       </c>
       <c r="N18" t="n">
-        <v>13.67048021441176</v>
+        <v>13.66066951663225</v>
       </c>
       <c r="O18" t="n">
-        <v>3.697361250190703</v>
+        <v>3.696034295922083</v>
       </c>
       <c r="P18" t="n">
-        <v>382.7154738214437</v>
+        <v>382.6868551669772</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30735,28 +30844,28 @@
         <v>0.1031</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1587178007655496</v>
+        <v>0.1603727388557639</v>
       </c>
       <c r="J19" t="n">
+        <v>264</v>
+      </c>
+      <c r="K19" t="n">
         <v>263</v>
       </c>
-      <c r="K19" t="n">
-        <v>262</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.07499248913695922</v>
+        <v>0.07695994505817161</v>
       </c>
       <c r="M19" t="n">
-        <v>3.051497258332982</v>
+        <v>3.048706312720201</v>
       </c>
       <c r="N19" t="n">
-        <v>15.81438111203786</v>
+        <v>15.77096787618989</v>
       </c>
       <c r="O19" t="n">
-        <v>3.976729952113653</v>
+        <v>3.971267792052041</v>
       </c>
       <c r="P19" t="n">
-        <v>381.284467386074</v>
+        <v>381.2664479316824</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30813,28 +30922,28 @@
         <v>0.1098</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1600179356331015</v>
+        <v>0.1605576124297453</v>
       </c>
       <c r="J20" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K20" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L20" t="n">
-        <v>0.07615099617351628</v>
+        <v>0.07721075851398695</v>
       </c>
       <c r="M20" t="n">
-        <v>3.103880157029238</v>
+        <v>3.094670485157862</v>
       </c>
       <c r="N20" t="n">
-        <v>15.83396137394551</v>
+        <v>15.77576338283948</v>
       </c>
       <c r="O20" t="n">
-        <v>3.979191045168038</v>
+        <v>3.971871521441685</v>
       </c>
       <c r="P20" t="n">
-        <v>377.918961405518</v>
+        <v>377.9130986256736</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30891,28 +31000,28 @@
         <v>0.0916</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1124832287767947</v>
+        <v>0.1116231560498217</v>
       </c>
       <c r="J21" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K21" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03923780340518979</v>
+        <v>0.03896386440875022</v>
       </c>
       <c r="M21" t="n">
-        <v>3.229388992958773</v>
+        <v>3.220908611362925</v>
       </c>
       <c r="N21" t="n">
-        <v>15.79114481237097</v>
+        <v>15.73584855253153</v>
       </c>
       <c r="O21" t="n">
-        <v>3.973807344647066</v>
+        <v>3.966843651132664</v>
       </c>
       <c r="P21" t="n">
-        <v>377.8738561209042</v>
+        <v>377.88319952251</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -30969,28 +31078,28 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.154264876884515</v>
+        <v>0.1535425088783815</v>
       </c>
       <c r="J22" t="n">
+        <v>264</v>
+      </c>
+      <c r="K22" t="n">
         <v>263</v>
       </c>
-      <c r="K22" t="n">
-        <v>262</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.05819802848836775</v>
+        <v>0.05813436566993546</v>
       </c>
       <c r="M22" t="n">
-        <v>3.534760195798719</v>
+        <v>3.523838179738881</v>
       </c>
       <c r="N22" t="n">
-        <v>19.41169193678324</v>
+        <v>19.34102035275419</v>
       </c>
       <c r="O22" t="n">
-        <v>4.405870167944493</v>
+        <v>4.397842693043282</v>
       </c>
       <c r="P22" t="n">
-        <v>376.8507155387206</v>
+        <v>376.8586228745485</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -31047,28 +31156,28 @@
         <v>0.09669999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2691911107062904</v>
+        <v>0.2659265738956086</v>
       </c>
       <c r="J23" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K23" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1404227396252135</v>
+        <v>0.1381614272571475</v>
       </c>
       <c r="M23" t="n">
-        <v>3.831720616982156</v>
+        <v>3.831322420322538</v>
       </c>
       <c r="N23" t="n">
-        <v>22.12377702281081</v>
+        <v>22.10226298672874</v>
       </c>
       <c r="O23" t="n">
-        <v>4.703591927751685</v>
+        <v>4.70130439205214</v>
       </c>
       <c r="P23" t="n">
-        <v>374.9213551311474</v>
+        <v>374.9574039010784</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -31125,28 +31234,28 @@
         <v>0.0977</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2968213320714133</v>
+        <v>0.2972060434303652</v>
       </c>
       <c r="J24" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K24" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2090081242154522</v>
+        <v>0.2108305348567046</v>
       </c>
       <c r="M24" t="n">
-        <v>3.257987086621107</v>
+        <v>3.24765789710224</v>
       </c>
       <c r="N24" t="n">
-        <v>16.55411839903357</v>
+        <v>16.49180465079343</v>
       </c>
       <c r="O24" t="n">
-        <v>4.068675263403749</v>
+        <v>4.061010299272022</v>
       </c>
       <c r="P24" t="n">
-        <v>375.0224767193758</v>
+        <v>375.0182251480575</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -31203,28 +31312,28 @@
         <v>0.0916</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3009278839776252</v>
+        <v>0.3005556378392902</v>
       </c>
       <c r="J25" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K25" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1453415868985617</v>
+        <v>0.1460814835270094</v>
       </c>
       <c r="M25" t="n">
-        <v>4.100297470965694</v>
+        <v>4.086308728089793</v>
       </c>
       <c r="N25" t="n">
-        <v>26.43836044928844</v>
+        <v>26.33826512689036</v>
       </c>
       <c r="O25" t="n">
-        <v>5.141824622572073</v>
+        <v>5.132081948575096</v>
       </c>
       <c r="P25" t="n">
-        <v>375.3268113270622</v>
+        <v>375.3309251411419</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -31281,28 +31390,28 @@
         <v>0.1013</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1858055825311129</v>
+        <v>0.1820650602663837</v>
       </c>
       <c r="J26" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K26" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L26" t="n">
-        <v>0.06655869072128895</v>
+        <v>0.06437764771120669</v>
       </c>
       <c r="M26" t="n">
-        <v>3.794662939253351</v>
+        <v>3.795735428550177</v>
       </c>
       <c r="N26" t="n">
-        <v>24.03846572054942</v>
+        <v>24.02895312021298</v>
       </c>
       <c r="O26" t="n">
-        <v>4.902903804945536</v>
+        <v>4.901933610343267</v>
       </c>
       <c r="P26" t="n">
-        <v>373.2267635076326</v>
+        <v>373.2681012451502</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -31359,28 +31468,28 @@
         <v>0.1481</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2700787733050514</v>
+        <v>0.2637676691065028</v>
       </c>
       <c r="J27" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K27" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L27" t="n">
-        <v>0.09695994644928818</v>
+        <v>0.09302455915069663</v>
       </c>
       <c r="M27" t="n">
-        <v>4.539005159482465</v>
+        <v>4.553630495081565</v>
       </c>
       <c r="N27" t="n">
-        <v>33.72892762685336</v>
+        <v>33.83429852697463</v>
       </c>
       <c r="O27" t="n">
-        <v>5.807661115014663</v>
+        <v>5.816725756555368</v>
       </c>
       <c r="P27" t="n">
-        <v>372.3056559731176</v>
+        <v>372.3754020541036</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -31437,28 +31546,28 @@
         <v>0.0771</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2525019770589818</v>
+        <v>0.2507747413476919</v>
       </c>
       <c r="J28" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K28" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L28" t="n">
-        <v>0.066811287568602</v>
+        <v>0.06645972526042543</v>
       </c>
       <c r="M28" t="n">
-        <v>5.355632839927268</v>
+        <v>5.343263337787903</v>
       </c>
       <c r="N28" t="n">
-        <v>43.87297639320405</v>
+        <v>43.72223533505491</v>
       </c>
       <c r="O28" t="n">
-        <v>6.623667895751119</v>
+        <v>6.612279133177524</v>
       </c>
       <c r="P28" t="n">
-        <v>377.4876724258987</v>
+        <v>377.5068682280976</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -31515,28 +31624,28 @@
         <v>0.123</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2684220205494399</v>
+        <v>0.2693386862372067</v>
       </c>
       <c r="J29" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K29" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L29" t="n">
-        <v>0.09707907097747026</v>
+        <v>0.09841447756417665</v>
       </c>
       <c r="M29" t="n">
-        <v>4.632166408684973</v>
+        <v>4.618379832759925</v>
       </c>
       <c r="N29" t="n">
-        <v>33.01477086845996</v>
+        <v>32.89316552799758</v>
       </c>
       <c r="O29" t="n">
-        <v>5.745848141785507</v>
+        <v>5.735256361140065</v>
       </c>
       <c r="P29" t="n">
-        <v>388.8584881789893</v>
+        <v>388.848300725644</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -31597,28 +31706,28 @@
         <v>0.1952</v>
       </c>
       <c r="I30" t="n">
-        <v>0.01904962490302249</v>
+        <v>0.01733529147294992</v>
       </c>
       <c r="J30" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K30" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0003620212240713627</v>
+        <v>0.0003023013662736274</v>
       </c>
       <c r="M30" t="n">
-        <v>5.279204333814535</v>
+        <v>5.266535042223993</v>
       </c>
       <c r="N30" t="n">
-        <v>47.81586695458208</v>
+        <v>47.64754526559012</v>
       </c>
       <c r="O30" t="n">
-        <v>6.914901803683266</v>
+        <v>6.902720135250314</v>
       </c>
       <c r="P30" t="n">
-        <v>397.3379957627512</v>
+        <v>397.3574184260344</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -31660,7 +31769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE264"/>
+  <dimension ref="A1:AE265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72987,6 +73096,163 @@
         </is>
       </c>
     </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>-35.694540896031754,174.51474167126565</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>-35.695262093176325,174.51488306838414</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>-35.69599452998641,174.51476663765976</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>-35.69671982908759,174.51485124001618</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>-35.69743233505057,174.51505256140456</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>-35.69813186163394,174.5153073903429</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>-35.69882485608761,174.5155885317698</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>-35.69949363160011,174.5159552081647</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>-35.70017392823866,174.5162743426177</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>-35.700847469879065,174.51662291613613</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>-35.701516461414194,174.5169872207006</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>-35.702190558492774,174.51730904357584</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>-35.70285865579126,174.5176448868106</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>-35.703543515046746,174.5179538388103</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>-35.70420811965752,174.51831393093875</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>-35.70485535283441,174.5186955188993</t>
+        </is>
+      </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>-35.70551345252116,174.5190557367704</t>
+        </is>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>-35.70615329504889,174.51946476843648</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>-35.706794706456904,174.51988260985596</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>-35.70743291018526,174.52031975540248</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>-35.70805480455519,174.5207879402058</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>-35.708685280247124,174.52123912642332</t>
+        </is>
+      </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>-35.70927830449486,174.52176138474874</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>-35.70988769462374,174.52223279916018</t>
+        </is>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>-35.710511054975086,174.5226936698893</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>-35.71109972287934,174.52322494441987</t>
+        </is>
+      </c>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>-35.71161886119139,174.52386325793782</t>
+        </is>
+      </c>
+      <c r="AC265" t="inlineStr">
+        <is>
+          <t>-35.71210610766112,174.5245458916862</t>
+        </is>
+      </c>
+      <c r="AD265" t="inlineStr">
+        <is>
+          <t>-35.71268161926417,174.52509503335241</t>
+        </is>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0097/nzd0097.xlsx
+++ b/data/nzd0097/nzd0097.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE265"/>
+  <dimension ref="A1:AE266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26657,6 +26657,105 @@
         <v>395.77</v>
       </c>
       <c r="AE265" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>393.4</v>
+      </c>
+      <c r="C266" t="n">
+        <v>396.77</v>
+      </c>
+      <c r="D266" t="n">
+        <v>379.29</v>
+      </c>
+      <c r="E266" t="n">
+        <v>365.05</v>
+      </c>
+      <c r="F266" t="n">
+        <v>361.43</v>
+      </c>
+      <c r="G266" t="n">
+        <v>360.29</v>
+      </c>
+      <c r="H266" t="n">
+        <v>362.3</v>
+      </c>
+      <c r="I266" t="n">
+        <v>373.28</v>
+      </c>
+      <c r="J266" t="n">
+        <v>374.51</v>
+      </c>
+      <c r="K266" t="n">
+        <v>382.48</v>
+      </c>
+      <c r="L266" t="n">
+        <v>389.38</v>
+      </c>
+      <c r="M266" t="n">
+        <v>392.57</v>
+      </c>
+      <c r="N266" t="n">
+        <v>392.69</v>
+      </c>
+      <c r="O266" t="n">
+        <v>389.99</v>
+      </c>
+      <c r="P266" t="n">
+        <v>391.7</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>394.11</v>
+      </c>
+      <c r="R266" t="n">
+        <v>389.81</v>
+      </c>
+      <c r="S266" t="n">
+        <v>388.85</v>
+      </c>
+      <c r="T266" t="n">
+        <v>383.55</v>
+      </c>
+      <c r="U266" t="n">
+        <v>380.43</v>
+      </c>
+      <c r="V266" t="n">
+        <v>379.77</v>
+      </c>
+      <c r="W266" t="n">
+        <v>378.28</v>
+      </c>
+      <c r="X266" t="n">
+        <v>383.5</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>384.24</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>374.99</v>
+      </c>
+      <c r="AA266" t="n">
+        <v>373.76</v>
+      </c>
+      <c r="AB266" t="n">
+        <v>384.07</v>
+      </c>
+      <c r="AC266" t="n">
+        <v>397.31</v>
+      </c>
+      <c r="AD266" t="n">
+        <v>396.82</v>
+      </c>
+      <c r="AE266" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26673,7 +26772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B267"/>
+  <dimension ref="A1:B268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29346,6 +29445,16 @@
       </c>
       <c r="B267" t="n">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>0.74</v>
       </c>
     </row>
   </sheetData>
@@ -29514,28 +29623,28 @@
         <v>0.0566</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07295888682564766</v>
+        <v>0.07380576931274915</v>
       </c>
       <c r="J2" t="n">
+        <v>265</v>
+      </c>
+      <c r="K2" t="n">
         <v>264</v>
       </c>
-      <c r="K2" t="n">
-        <v>263</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.006957494869637926</v>
+        <v>0.007177217600105146</v>
       </c>
       <c r="M2" t="n">
-        <v>4.41218563534273</v>
+        <v>4.399636998344461</v>
       </c>
       <c r="N2" t="n">
-        <v>38.84820456673114</v>
+        <v>38.70544823795841</v>
       </c>
       <c r="O2" t="n">
-        <v>6.232832788285848</v>
+        <v>6.221370286195672</v>
       </c>
       <c r="P2" t="n">
-        <v>390.3964484125538</v>
+        <v>390.3871942270924</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -29596,28 +29705,28 @@
         <v>0.0609</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02635643911265747</v>
+        <v>-0.02905429880533555</v>
       </c>
       <c r="J3" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K3" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001143338170628838</v>
+        <v>0.001398640499882475</v>
       </c>
       <c r="M3" t="n">
-        <v>4.42538732105618</v>
+        <v>4.420821370244868</v>
       </c>
       <c r="N3" t="n">
-        <v>30.9824533473105</v>
+        <v>30.90922178650679</v>
       </c>
       <c r="O3" t="n">
-        <v>5.566188403864039</v>
+        <v>5.559606261823475</v>
       </c>
       <c r="P3" t="n">
-        <v>400.9084778707686</v>
+        <v>400.9380266261435</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29674,28 +29783,28 @@
         <v>0.132</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00333957442832328</v>
+        <v>0.0006000682307778467</v>
       </c>
       <c r="J4" t="n">
+        <v>265</v>
+      </c>
+      <c r="K4" t="n">
         <v>264</v>
       </c>
-      <c r="K4" t="n">
-        <v>263</v>
-      </c>
       <c r="L4" t="n">
-        <v>3.051954565769233e-05</v>
+        <v>9.912031843084534e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>3.383171424224682</v>
+        <v>3.384783070356079</v>
       </c>
       <c r="N4" t="n">
-        <v>18.68238817646026</v>
+        <v>18.65761216574052</v>
       </c>
       <c r="O4" t="n">
-        <v>4.322312827232691</v>
+        <v>4.319445816970103</v>
       </c>
       <c r="P4" t="n">
-        <v>382.7038677119104</v>
+        <v>382.7338056412431</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29752,28 +29861,28 @@
         <v>0.1347</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09084650474786883</v>
+        <v>0.08928762882125214</v>
       </c>
       <c r="J5" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K5" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01955625233898117</v>
+        <v>0.01904576987093198</v>
       </c>
       <c r="M5" t="n">
-        <v>3.544933429182691</v>
+        <v>3.539243007771055</v>
       </c>
       <c r="N5" t="n">
-        <v>21.18640997332978</v>
+        <v>21.12136524210072</v>
       </c>
       <c r="O5" t="n">
-        <v>4.602869754113164</v>
+        <v>4.595798651170514</v>
       </c>
       <c r="P5" t="n">
-        <v>364.657480494509</v>
+        <v>364.6744773038618</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29830,28 +29939,28 @@
         <v>0.114</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2383877133481395</v>
+        <v>0.2349407300168542</v>
       </c>
       <c r="J6" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K6" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1048837738352838</v>
+        <v>0.1026777071641264</v>
       </c>
       <c r="M6" t="n">
-        <v>3.832071797528006</v>
+        <v>3.836598554539265</v>
       </c>
       <c r="N6" t="n">
-        <v>24.83377474829978</v>
+        <v>24.81293388746245</v>
       </c>
       <c r="O6" t="n">
-        <v>4.983349751753311</v>
+        <v>4.981258263477457</v>
       </c>
       <c r="P6" t="n">
-        <v>359.5683942541908</v>
+        <v>359.6059775650392</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29908,28 +30017,28 @@
         <v>0.1066</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2160390675188502</v>
+        <v>0.2089218100515125</v>
       </c>
       <c r="J7" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K7" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1083824444526689</v>
+        <v>0.10140090280831</v>
       </c>
       <c r="M7" t="n">
-        <v>3.466075783016788</v>
+        <v>3.489552255625799</v>
       </c>
       <c r="N7" t="n">
-        <v>19.66020919813571</v>
+        <v>19.89669356307578</v>
       </c>
       <c r="O7" t="n">
-        <v>4.433983445857203</v>
+        <v>4.460570990700157</v>
       </c>
       <c r="P7" t="n">
-        <v>363.7165582262575</v>
+        <v>363.7941594427632</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29986,28 +30095,28 @@
         <v>0.1191</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1069348571792099</v>
+        <v>0.09837173856916903</v>
       </c>
       <c r="J8" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K8" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0290482829414308</v>
+        <v>0.02434692517444981</v>
       </c>
       <c r="M8" t="n">
-        <v>3.405943703158481</v>
+        <v>3.438443172009717</v>
       </c>
       <c r="N8" t="n">
-        <v>19.5712981417355</v>
+        <v>19.94716526363349</v>
       </c>
       <c r="O8" t="n">
-        <v>4.423945992181132</v>
+        <v>4.466224945480634</v>
       </c>
       <c r="P8" t="n">
-        <v>370.4644800316255</v>
+        <v>370.5578458293743</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30064,28 +30173,28 @@
         <v>0.1247</v>
       </c>
       <c r="I9" t="n">
-        <v>0.109731872965276</v>
+        <v>0.1060017884986017</v>
       </c>
       <c r="J9" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K9" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03323398828529467</v>
+        <v>0.03119022318153919</v>
       </c>
       <c r="M9" t="n">
-        <v>3.231455690377089</v>
+        <v>3.237228610516242</v>
       </c>
       <c r="N9" t="n">
-        <v>17.93528873833084</v>
+        <v>17.95294133306176</v>
       </c>
       <c r="O9" t="n">
-        <v>4.235007525179954</v>
+        <v>4.237091140518666</v>
       </c>
       <c r="P9" t="n">
-        <v>375.1691066264388</v>
+        <v>375.2097766589073</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30142,28 +30251,28 @@
         <v>0.1072</v>
       </c>
       <c r="I10" t="n">
-        <v>0.15590339767678</v>
+        <v>0.1506543111346038</v>
       </c>
       <c r="J10" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K10" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04787381196095941</v>
+        <v>0.04491177093774024</v>
       </c>
       <c r="M10" t="n">
-        <v>3.688328422422619</v>
+        <v>3.69930716310394</v>
       </c>
       <c r="N10" t="n">
-        <v>24.75207079191341</v>
+        <v>24.82765121933204</v>
       </c>
       <c r="O10" t="n">
-        <v>4.975145303598017</v>
+        <v>4.982735314998383</v>
       </c>
       <c r="P10" t="n">
-        <v>377.1362457386435</v>
+        <v>377.1934778260151</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30220,28 +30329,28 @@
         <v>0.1173</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1164483580562831</v>
+        <v>0.115694139245994</v>
       </c>
       <c r="J11" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K11" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0337975657297509</v>
+        <v>0.03364051522168621</v>
       </c>
       <c r="M11" t="n">
-        <v>3.592934562718146</v>
+        <v>3.582441194670773</v>
       </c>
       <c r="N11" t="n">
-        <v>19.84967141454111</v>
+        <v>19.77825577778892</v>
       </c>
       <c r="O11" t="n">
-        <v>4.455297006321925</v>
+        <v>4.447275095807423</v>
       </c>
       <c r="P11" t="n">
-        <v>380.3740171621104</v>
+        <v>380.3822405961309</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30298,28 +30407,28 @@
         <v>0.1139</v>
       </c>
       <c r="I12" t="n">
-        <v>0.05644834267466214</v>
+        <v>0.05984268273149552</v>
       </c>
       <c r="J12" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K12" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L12" t="n">
-        <v>0.00775246351453851</v>
+        <v>0.008747388209289886</v>
       </c>
       <c r="M12" t="n">
-        <v>3.510010540405987</v>
+        <v>3.51228723164041</v>
       </c>
       <c r="N12" t="n">
-        <v>20.88269602810083</v>
+        <v>20.87455606805098</v>
       </c>
       <c r="O12" t="n">
-        <v>4.569758858856868</v>
+        <v>4.568868138614966</v>
       </c>
       <c r="P12" t="n">
-        <v>383.5427615601811</v>
+        <v>383.5057522319598</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30376,28 +30485,28 @@
         <v>0.1126</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0469028848946361</v>
+        <v>0.04976504918724649</v>
       </c>
       <c r="J13" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K13" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L13" t="n">
-        <v>0.007058510558452191</v>
+        <v>0.007980071785626985</v>
       </c>
       <c r="M13" t="n">
-        <v>3.174034501707686</v>
+        <v>3.175362029345159</v>
       </c>
       <c r="N13" t="n">
-        <v>15.8457784192124</v>
+        <v>15.83622520507796</v>
       </c>
       <c r="O13" t="n">
-        <v>3.98067562346047</v>
+        <v>3.979475493714964</v>
       </c>
       <c r="P13" t="n">
-        <v>387.6608126412347</v>
+        <v>387.6296057568463</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30454,28 +30563,28 @@
         <v>0.1163</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1233734896908492</v>
+        <v>0.1266701629177218</v>
       </c>
       <c r="J14" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K14" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03660403788203137</v>
+        <v>0.03869915410710301</v>
       </c>
       <c r="M14" t="n">
-        <v>3.557786362641101</v>
+        <v>3.559018097422182</v>
       </c>
       <c r="N14" t="n">
-        <v>20.51272705944643</v>
+        <v>20.50197529551713</v>
       </c>
       <c r="O14" t="n">
-        <v>4.529097819593481</v>
+        <v>4.527910698712723</v>
       </c>
       <c r="P14" t="n">
-        <v>385.2118991260527</v>
+        <v>385.1759546834073</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30532,28 +30641,28 @@
         <v>0.1195</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1846046243149721</v>
+        <v>0.1866973927157016</v>
       </c>
       <c r="J15" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K15" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L15" t="n">
-        <v>0.06208330320536715</v>
+        <v>0.06384583595130811</v>
       </c>
       <c r="M15" t="n">
-        <v>3.676564080015345</v>
+        <v>3.671790423500654</v>
       </c>
       <c r="N15" t="n">
-        <v>26.36200756897388</v>
+        <v>26.28938926324448</v>
       </c>
       <c r="O15" t="n">
-        <v>5.134394566935217</v>
+        <v>5.127317940526458</v>
       </c>
       <c r="P15" t="n">
-        <v>382.4388237267492</v>
+        <v>382.4160057558515</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30610,28 +30719,28 @@
         <v>0.1336</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1265624278335981</v>
+        <v>0.1297029370124828</v>
       </c>
       <c r="J16" t="n">
+        <v>265</v>
+      </c>
+      <c r="K16" t="n">
         <v>264</v>
       </c>
-      <c r="K16" t="n">
-        <v>263</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.04815880088970426</v>
+        <v>0.05067742236957895</v>
       </c>
       <c r="M16" t="n">
-        <v>3.238440269295152</v>
+        <v>3.242861514937109</v>
       </c>
       <c r="N16" t="n">
-        <v>16.18818052819375</v>
+        <v>16.18731324665377</v>
       </c>
       <c r="O16" t="n">
-        <v>4.023453805897833</v>
+        <v>4.023346026214222</v>
       </c>
       <c r="P16" t="n">
-        <v>384.3457018534431</v>
+        <v>384.3113843952044</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30688,28 +30797,28 @@
         <v>0.1213</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0788208889373456</v>
+        <v>0.08407984537096073</v>
       </c>
       <c r="J17" t="n">
+        <v>265</v>
+      </c>
+      <c r="K17" t="n">
         <v>264</v>
       </c>
-      <c r="K17" t="n">
-        <v>263</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.01990569144195409</v>
+        <v>0.02253398591427636</v>
       </c>
       <c r="M17" t="n">
-        <v>3.234450531321882</v>
+        <v>3.249286303679308</v>
       </c>
       <c r="N17" t="n">
-        <v>15.63920645142341</v>
+        <v>15.74944910020012</v>
       </c>
       <c r="O17" t="n">
-        <v>3.954643656693155</v>
+        <v>3.968557559139104</v>
       </c>
       <c r="P17" t="n">
-        <v>385.3016456459844</v>
+        <v>385.2441746075124</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30766,28 +30875,28 @@
         <v>0.1036</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1135523764745687</v>
+        <v>0.1167767484031682</v>
       </c>
       <c r="J18" t="n">
+        <v>265</v>
+      </c>
+      <c r="K18" t="n">
         <v>264</v>
       </c>
-      <c r="K18" t="n">
-        <v>263</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.04603562903347469</v>
+        <v>0.04872848616758385</v>
       </c>
       <c r="M18" t="n">
-        <v>2.905972066984948</v>
+        <v>2.909399669052534</v>
       </c>
       <c r="N18" t="n">
-        <v>13.66066951663225</v>
+        <v>13.67263562200755</v>
       </c>
       <c r="O18" t="n">
-        <v>3.696034295922083</v>
+        <v>3.697652717874889</v>
       </c>
       <c r="P18" t="n">
-        <v>382.6868551669772</v>
+        <v>382.6516185177492</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30844,28 +30953,28 @@
         <v>0.1031</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1603727388557639</v>
+        <v>0.1629949736816378</v>
       </c>
       <c r="J19" t="n">
+        <v>265</v>
+      </c>
+      <c r="K19" t="n">
         <v>264</v>
       </c>
-      <c r="K19" t="n">
-        <v>263</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.07695994505817161</v>
+        <v>0.07971081833752047</v>
       </c>
       <c r="M19" t="n">
-        <v>3.048706312720201</v>
+        <v>3.050966636576192</v>
       </c>
       <c r="N19" t="n">
-        <v>15.77096787618989</v>
+        <v>15.753366764745</v>
       </c>
       <c r="O19" t="n">
-        <v>3.971267792052041</v>
+        <v>3.969051116418759</v>
       </c>
       <c r="P19" t="n">
-        <v>381.2664479316824</v>
+        <v>381.2377915698238</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30922,28 +31031,28 @@
         <v>0.1098</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1605576124297453</v>
+        <v>0.161648420752494</v>
       </c>
       <c r="J20" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K20" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L20" t="n">
-        <v>0.07721075851398695</v>
+        <v>0.07875150672941256</v>
       </c>
       <c r="M20" t="n">
-        <v>3.094670485157862</v>
+        <v>3.088081777136042</v>
       </c>
       <c r="N20" t="n">
-        <v>15.77576338283948</v>
+        <v>15.72352973563595</v>
       </c>
       <c r="O20" t="n">
-        <v>3.971871521441685</v>
+        <v>3.965290624359827</v>
       </c>
       <c r="P20" t="n">
-        <v>377.9130986256736</v>
+        <v>377.9012052730433</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31000,28 +31109,28 @@
         <v>0.0916</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1116231560498217</v>
+        <v>0.1113157289619802</v>
       </c>
       <c r="J21" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K21" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03896386440875022</v>
+        <v>0.03906881807808771</v>
       </c>
       <c r="M21" t="n">
-        <v>3.220908611362925</v>
+        <v>3.210078186644508</v>
       </c>
       <c r="N21" t="n">
-        <v>15.73584855253153</v>
+        <v>15.67704763894638</v>
       </c>
       <c r="O21" t="n">
-        <v>3.966843651132664</v>
+        <v>3.95942516521608</v>
       </c>
       <c r="P21" t="n">
-        <v>377.88319952251</v>
+        <v>377.8865514759996</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -31078,28 +31187,28 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1535425088783815</v>
+        <v>0.1526457555192546</v>
       </c>
       <c r="J22" t="n">
+        <v>265</v>
+      </c>
+      <c r="K22" t="n">
         <v>264</v>
       </c>
-      <c r="K22" t="n">
-        <v>263</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.05813436566993546</v>
+        <v>0.05793894330481963</v>
       </c>
       <c r="M22" t="n">
-        <v>3.523838179738881</v>
+        <v>3.513571323348022</v>
       </c>
       <c r="N22" t="n">
-        <v>19.34102035275419</v>
+        <v>19.27261296135371</v>
       </c>
       <c r="O22" t="n">
-        <v>4.397842693043282</v>
+        <v>4.390058423455628</v>
       </c>
       <c r="P22" t="n">
-        <v>376.8586228745485</v>
+        <v>376.8684747098814</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -31156,28 +31265,28 @@
         <v>0.09669999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2659265738956086</v>
+        <v>0.2629891988466274</v>
       </c>
       <c r="J23" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K23" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1381614272571475</v>
+        <v>0.1362513974513904</v>
       </c>
       <c r="M23" t="n">
-        <v>3.831322420322538</v>
+        <v>3.829670005611907</v>
       </c>
       <c r="N23" t="n">
-        <v>22.10226298672874</v>
+        <v>22.06931472681757</v>
       </c>
       <c r="O23" t="n">
-        <v>4.70130439205214</v>
+        <v>4.69779892362557</v>
       </c>
       <c r="P23" t="n">
-        <v>374.9574039010784</v>
+        <v>374.9899572272698</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -31234,28 +31343,28 @@
         <v>0.0977</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2972060434303652</v>
+        <v>0.2977169412487028</v>
       </c>
       <c r="J24" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K24" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2108305348567046</v>
+        <v>0.2127999625476498</v>
       </c>
       <c r="M24" t="n">
-        <v>3.24765789710224</v>
+        <v>3.238075997805252</v>
       </c>
       <c r="N24" t="n">
-        <v>16.49180465079343</v>
+        <v>16.43063857346266</v>
       </c>
       <c r="O24" t="n">
-        <v>4.061010299272022</v>
+        <v>4.053472409362453</v>
       </c>
       <c r="P24" t="n">
-        <v>375.0182251480575</v>
+        <v>375.0125588376658</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -31312,28 +31421,28 @@
         <v>0.0916</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3005556378392902</v>
+        <v>0.3013409415863693</v>
       </c>
       <c r="J25" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K25" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1460814835270094</v>
+        <v>0.1477780233517323</v>
       </c>
       <c r="M25" t="n">
-        <v>4.086308728089793</v>
+        <v>4.074704415530214</v>
       </c>
       <c r="N25" t="n">
-        <v>26.33826512689036</v>
+        <v>26.24175913397399</v>
       </c>
       <c r="O25" t="n">
-        <v>5.132081948575096</v>
+        <v>5.122671093675055</v>
       </c>
       <c r="P25" t="n">
-        <v>375.3309251411419</v>
+        <v>375.322215425377</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -31390,28 +31499,28 @@
         <v>0.1013</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1820650602663837</v>
+        <v>0.1796104657215147</v>
       </c>
       <c r="J26" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K26" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L26" t="n">
-        <v>0.06437764771120669</v>
+        <v>0.06317299229935103</v>
       </c>
       <c r="M26" t="n">
-        <v>3.795735428550177</v>
+        <v>3.791377711514524</v>
       </c>
       <c r="N26" t="n">
-        <v>24.02895312021298</v>
+        <v>23.97314536331109</v>
       </c>
       <c r="O26" t="n">
-        <v>4.901933610343267</v>
+        <v>4.896237878546251</v>
       </c>
       <c r="P26" t="n">
-        <v>373.2681012451502</v>
+        <v>373.2953248778956</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -31468,28 +31577,28 @@
         <v>0.1481</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2637676691065028</v>
+        <v>0.2593261356658926</v>
       </c>
       <c r="J27" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K27" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L27" t="n">
-        <v>0.09302455915069663</v>
+        <v>0.0906100367848508</v>
       </c>
       <c r="M27" t="n">
-        <v>4.553630495081565</v>
+        <v>4.558696807601475</v>
       </c>
       <c r="N27" t="n">
-        <v>33.83429852697463</v>
+        <v>33.82207231336572</v>
       </c>
       <c r="O27" t="n">
-        <v>5.816725756555368</v>
+        <v>5.815674708352052</v>
       </c>
       <c r="P27" t="n">
-        <v>372.3754020541036</v>
+        <v>372.4246626032506</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -31546,28 +31655,28 @@
         <v>0.0771</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2507747413476919</v>
+        <v>0.2507375480075499</v>
       </c>
       <c r="J28" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K28" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L28" t="n">
-        <v>0.06645972526042543</v>
+        <v>0.06696908460092899</v>
       </c>
       <c r="M28" t="n">
-        <v>5.343263337787903</v>
+        <v>5.323043689770919</v>
       </c>
       <c r="N28" t="n">
-        <v>43.72223533505491</v>
+        <v>43.55536465399078</v>
       </c>
       <c r="O28" t="n">
-        <v>6.612279133177524</v>
+        <v>6.59964882808099</v>
       </c>
       <c r="P28" t="n">
-        <v>377.5068682280976</v>
+        <v>377.5072830530528</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -31624,28 +31733,28 @@
         <v>0.123</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2693386862372067</v>
+        <v>0.2704315215342158</v>
       </c>
       <c r="J29" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K29" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L29" t="n">
-        <v>0.09841447756417665</v>
+        <v>0.09987594386336862</v>
       </c>
       <c r="M29" t="n">
-        <v>4.618379832759925</v>
+        <v>4.605414910864929</v>
       </c>
       <c r="N29" t="n">
-        <v>32.89316552799758</v>
+        <v>32.77459462687806</v>
       </c>
       <c r="O29" t="n">
-        <v>5.735256361140065</v>
+        <v>5.724910010373792</v>
       </c>
       <c r="P29" t="n">
-        <v>388.848300725644</v>
+        <v>388.8361121093129</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -31706,28 +31815,28 @@
         <v>0.1952</v>
       </c>
       <c r="I30" t="n">
-        <v>0.01733529147294992</v>
+        <v>0.01651380714336668</v>
       </c>
       <c r="J30" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K30" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0003023013662736274</v>
+        <v>0.0002766881150991773</v>
       </c>
       <c r="M30" t="n">
-        <v>5.266535042223993</v>
+        <v>5.249928474012561</v>
       </c>
       <c r="N30" t="n">
-        <v>47.64754526559012</v>
+        <v>47.46804280886435</v>
       </c>
       <c r="O30" t="n">
-        <v>6.902720135250314</v>
+        <v>6.889705567646875</v>
       </c>
       <c r="P30" t="n">
-        <v>397.3574184260344</v>
+        <v>397.366757756292</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -31769,7 +31878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE265"/>
+  <dimension ref="A1:AE266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73253,6 +73362,163 @@
         </is>
       </c>
     </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>-35.69454037428508,174.5147473817423</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>-35.69526277546799,174.51487560077183</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>-35.695993641022795,174.51477216707536</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>-35.69671901799464,174.51485463355442</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>-35.69742882851987,174.51506684717447</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>-35.69813235514857,174.5153053797367</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>-35.698827701915484,174.5155772336607</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>-35.69949363160011,174.5159552081647</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>-35.70017832162785,174.51625913351927</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>-35.70084428013324,174.51663395843832</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>-35.70151345219632,174.51699763804217</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>-35.702187235453756,174.51731967249367</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>-35.70285615680357,174.5176522304103</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>-35.70353959461016,174.5179652452572</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>-35.70420526764817,174.51832193099975</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>-35.70485246729274,174.51870276965758</t>
+        </is>
+      </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t>-35.70550990353596,174.5190638121516</t>
+        </is>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>-35.70614745829447,174.51947697141472</t>
+        </is>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>-35.70679119239226,174.51988956148656</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>-35.70742958605483,174.5203263313087</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>-35.70805585479224,174.5207858776794</t>
+        </is>
+      </c>
+      <c r="W266" t="inlineStr">
+        <is>
+          <t>-35.70868350146248,174.52124258564655</t>
+        </is>
+      </c>
+      <c r="X266" t="inlineStr">
+        <is>
+          <t>-35.70927733102078,174.52176324527946</t>
+        </is>
+      </c>
+      <c r="Y266" t="inlineStr">
+        <is>
+          <t>-35.709879981874906,174.52224601052072</t>
+        </is>
+      </c>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t>-35.710502429393436,174.522707147086</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>-35.71108725746759,174.52324442122642</t>
+        </is>
+      </c>
+      <c r="AB266" t="inlineStr">
+        <is>
+          <t>-35.71160716384074,174.5238813661518</t>
+        </is>
+      </c>
+      <c r="AC266" t="inlineStr">
+        <is>
+          <t>-35.712104635182335,174.52454812742502</t>
+        </is>
+      </c>
+      <c r="AD266" t="inlineStr">
+        <is>
+          <t>-35.71267563632772,174.52510402614638</t>
+        </is>
+      </c>
+      <c r="AE266" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0097/nzd0097.xlsx
+++ b/data/nzd0097/nzd0097.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE266"/>
+  <dimension ref="A1:AE269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26690,7 +26690,7 @@
         <v>362.3</v>
       </c>
       <c r="I266" t="n">
-        <v>373.28</v>
+        <v>368.77</v>
       </c>
       <c r="J266" t="n">
         <v>374.51</v>
@@ -26756,6 +26756,303 @@
         <v>396.82</v>
       </c>
       <c r="AE266" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>397.07</v>
+      </c>
+      <c r="C267" t="n">
+        <v>398.06</v>
+      </c>
+      <c r="D267" t="n">
+        <v>379.71</v>
+      </c>
+      <c r="E267" t="n">
+        <v>366.01</v>
+      </c>
+      <c r="F267" t="n">
+        <v>361.38</v>
+      </c>
+      <c r="G267" t="n">
+        <v>361.53</v>
+      </c>
+      <c r="H267" t="n">
+        <v>365</v>
+      </c>
+      <c r="I267" t="n">
+        <v>367.07</v>
+      </c>
+      <c r="J267" t="n">
+        <v>375.15</v>
+      </c>
+      <c r="K267" t="n">
+        <v>384.34</v>
+      </c>
+      <c r="L267" t="n">
+        <v>389.95</v>
+      </c>
+      <c r="M267" t="n">
+        <v>395.99</v>
+      </c>
+      <c r="N267" t="n">
+        <v>394.38</v>
+      </c>
+      <c r="O267" t="n">
+        <v>389.24</v>
+      </c>
+      <c r="P267" t="n">
+        <v>391.9</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>395.68</v>
+      </c>
+      <c r="R267" t="n">
+        <v>393.74</v>
+      </c>
+      <c r="S267" t="n">
+        <v>394.5</v>
+      </c>
+      <c r="T267" t="n">
+        <v>387.44</v>
+      </c>
+      <c r="U267" t="n">
+        <v>385.37</v>
+      </c>
+      <c r="V267" t="n">
+        <v>383.45</v>
+      </c>
+      <c r="W267" t="n">
+        <v>382.39</v>
+      </c>
+      <c r="X267" t="n">
+        <v>385.93</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>388.33</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>379.23</v>
+      </c>
+      <c r="AA267" t="n">
+        <v>382.02</v>
+      </c>
+      <c r="AB267" t="n">
+        <v>391.65</v>
+      </c>
+      <c r="AC267" t="n">
+        <v>399.08</v>
+      </c>
+      <c r="AD267" t="n">
+        <v>398.02</v>
+      </c>
+      <c r="AE267" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>397.2</v>
+      </c>
+      <c r="C268" t="n">
+        <v>400.32</v>
+      </c>
+      <c r="D268" t="n">
+        <v>379.93</v>
+      </c>
+      <c r="E268" t="n">
+        <v>365.19</v>
+      </c>
+      <c r="F268" t="n">
+        <v>361.37</v>
+      </c>
+      <c r="G268" t="n">
+        <v>361.76</v>
+      </c>
+      <c r="H268" t="n">
+        <v>365.08</v>
+      </c>
+      <c r="I268" t="n">
+        <v>367.16</v>
+      </c>
+      <c r="J268" t="n">
+        <v>375.44</v>
+      </c>
+      <c r="K268" t="n">
+        <v>384.52</v>
+      </c>
+      <c r="L268" t="n">
+        <v>389.27</v>
+      </c>
+      <c r="M268" t="n">
+        <v>395.66</v>
+      </c>
+      <c r="N268" t="n">
+        <v>395.58</v>
+      </c>
+      <c r="O268" t="n">
+        <v>390.53</v>
+      </c>
+      <c r="P268" t="n">
+        <v>393.46</v>
+      </c>
+      <c r="Q268" t="n">
+        <v>396.12</v>
+      </c>
+      <c r="R268" t="n">
+        <v>393.94</v>
+      </c>
+      <c r="S268" t="n">
+        <v>394.19</v>
+      </c>
+      <c r="T268" t="n">
+        <v>388.2</v>
+      </c>
+      <c r="U268" t="n">
+        <v>385.24</v>
+      </c>
+      <c r="V268" t="n">
+        <v>383.17</v>
+      </c>
+      <c r="W268" t="n">
+        <v>382.42</v>
+      </c>
+      <c r="X268" t="n">
+        <v>385.65</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>387.36</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>379.68</v>
+      </c>
+      <c r="AA268" t="n">
+        <v>381.07</v>
+      </c>
+      <c r="AB268" t="n">
+        <v>389.36</v>
+      </c>
+      <c r="AC268" t="n">
+        <v>397.71</v>
+      </c>
+      <c r="AD268" t="n">
+        <v>398.46</v>
+      </c>
+      <c r="AE268" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>397.98</v>
+      </c>
+      <c r="C269" t="n">
+        <v>402.39</v>
+      </c>
+      <c r="D269" t="n">
+        <v>380.46</v>
+      </c>
+      <c r="E269" t="n">
+        <v>364.63</v>
+      </c>
+      <c r="F269" t="n">
+        <v>361.49</v>
+      </c>
+      <c r="G269" t="n">
+        <v>361.38</v>
+      </c>
+      <c r="H269" t="n">
+        <v>364.4</v>
+      </c>
+      <c r="I269" t="n">
+        <v>368.17</v>
+      </c>
+      <c r="J269" t="n">
+        <v>375.75</v>
+      </c>
+      <c r="K269" t="n">
+        <v>384.19</v>
+      </c>
+      <c r="L269" t="n">
+        <v>389.42</v>
+      </c>
+      <c r="M269" t="n">
+        <v>395.86</v>
+      </c>
+      <c r="N269" t="n">
+        <v>394.66</v>
+      </c>
+      <c r="O269" t="n">
+        <v>390.05</v>
+      </c>
+      <c r="P269" t="n">
+        <v>392.71</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>396.63</v>
+      </c>
+      <c r="R269" t="n">
+        <v>394.29</v>
+      </c>
+      <c r="S269" t="n">
+        <v>393.61</v>
+      </c>
+      <c r="T269" t="n">
+        <v>387.98</v>
+      </c>
+      <c r="U269" t="n">
+        <v>385.38</v>
+      </c>
+      <c r="V269" t="n">
+        <v>383.4</v>
+      </c>
+      <c r="W269" t="n">
+        <v>382.63</v>
+      </c>
+      <c r="X269" t="n">
+        <v>385.48</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>386.77</v>
+      </c>
+      <c r="Z269" t="n">
+        <v>380.4</v>
+      </c>
+      <c r="AA269" t="n">
+        <v>380.35</v>
+      </c>
+      <c r="AB269" t="n">
+        <v>388.13</v>
+      </c>
+      <c r="AC269" t="n">
+        <v>397.28</v>
+      </c>
+      <c r="AD269" t="n">
+        <v>397.74</v>
+      </c>
+      <c r="AE269" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26772,7 +27069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B268"/>
+  <dimension ref="A1:B271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29455,6 +29752,36 @@
       </c>
       <c r="B268" t="n">
         <v>0.74</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>-0.63</v>
       </c>
     </row>
   </sheetData>
@@ -29623,28 +29950,28 @@
         <v>0.0566</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07380576931274915</v>
+        <v>0.08550680932018381</v>
       </c>
       <c r="J2" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K2" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007177217600105146</v>
+        <v>0.009782620629213867</v>
       </c>
       <c r="M2" t="n">
-        <v>4.399636998344461</v>
+        <v>4.407328154226184</v>
       </c>
       <c r="N2" t="n">
-        <v>38.70544823795841</v>
+        <v>38.55063311629959</v>
       </c>
       <c r="O2" t="n">
-        <v>6.221370286195672</v>
+        <v>6.208915615169817</v>
       </c>
       <c r="P2" t="n">
-        <v>390.3871942270924</v>
+        <v>390.2581352827073</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -29705,28 +30032,28 @@
         <v>0.0609</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02905429880533555</v>
+        <v>-0.02883222267367242</v>
       </c>
       <c r="J3" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K3" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001398640499882475</v>
+        <v>0.001410955985712947</v>
       </c>
       <c r="M3" t="n">
-        <v>4.420821370244868</v>
+        <v>4.387878405627534</v>
       </c>
       <c r="N3" t="n">
-        <v>30.90922178650679</v>
+        <v>30.59596411479209</v>
       </c>
       <c r="O3" t="n">
-        <v>5.559606261823475</v>
+        <v>5.531361868002499</v>
       </c>
       <c r="P3" t="n">
-        <v>400.9380266261435</v>
+        <v>400.9355218208671</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29783,28 +30110,28 @@
         <v>0.132</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006000682307778467</v>
+        <v>-0.005666645589536958</v>
       </c>
       <c r="J4" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K4" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="L4" t="n">
-        <v>9.912031843084534e-07</v>
+        <v>9.025253535510647e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.384783070356079</v>
+        <v>3.379793241491447</v>
       </c>
       <c r="N4" t="n">
-        <v>18.65761216574052</v>
+        <v>18.52895660092232</v>
       </c>
       <c r="O4" t="n">
-        <v>4.319445816970103</v>
+        <v>4.304527453846975</v>
       </c>
       <c r="P4" t="n">
-        <v>382.7338056412431</v>
+        <v>382.8029160054835</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29861,28 +30188,28 @@
         <v>0.1347</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08928762882125214</v>
+        <v>0.08519947136003031</v>
       </c>
       <c r="J5" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K5" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01904576987093198</v>
+        <v>0.01777724077871545</v>
       </c>
       <c r="M5" t="n">
-        <v>3.539243007771055</v>
+        <v>3.519382122513637</v>
       </c>
       <c r="N5" t="n">
-        <v>21.12136524210072</v>
+        <v>20.92250565386299</v>
       </c>
       <c r="O5" t="n">
-        <v>4.595798651170514</v>
+        <v>4.574112553694213</v>
       </c>
       <c r="P5" t="n">
-        <v>364.6744773038618</v>
+        <v>364.7194795919801</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29939,28 +30266,28 @@
         <v>0.114</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2349407300168542</v>
+        <v>0.2247174697650185</v>
       </c>
       <c r="J6" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K6" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1026777071641264</v>
+        <v>0.09620543710860296</v>
       </c>
       <c r="M6" t="n">
-        <v>3.836598554539265</v>
+        <v>3.849319075841921</v>
       </c>
       <c r="N6" t="n">
-        <v>24.81293388746245</v>
+        <v>24.74788190749372</v>
       </c>
       <c r="O6" t="n">
-        <v>4.981258263477457</v>
+        <v>4.97472430467194</v>
       </c>
       <c r="P6" t="n">
-        <v>359.6059775650392</v>
+        <v>359.7184748228167</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30017,28 +30344,28 @@
         <v>0.1066</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2089218100515125</v>
+        <v>0.1909677314717765</v>
       </c>
       <c r="J7" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K7" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L7" t="n">
-        <v>0.10140090280831</v>
+        <v>0.08557059547169599</v>
       </c>
       <c r="M7" t="n">
-        <v>3.489552255625799</v>
+        <v>3.54127468112407</v>
       </c>
       <c r="N7" t="n">
-        <v>19.89669356307578</v>
+        <v>20.33011625860507</v>
       </c>
       <c r="O7" t="n">
-        <v>4.460570990700157</v>
+        <v>4.508893019201617</v>
       </c>
       <c r="P7" t="n">
-        <v>363.7941594427632</v>
+        <v>363.9917317766481</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30095,28 +30422,28 @@
         <v>0.1191</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09837173856916903</v>
+        <v>0.07914972121313101</v>
       </c>
       <c r="J8" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K8" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02434692517444981</v>
+        <v>0.01570934285411318</v>
       </c>
       <c r="M8" t="n">
-        <v>3.438443172009717</v>
+        <v>3.499918935406412</v>
       </c>
       <c r="N8" t="n">
-        <v>19.94716526363349</v>
+        <v>20.47662509618243</v>
       </c>
       <c r="O8" t="n">
-        <v>4.466224945480634</v>
+        <v>4.525110506516103</v>
       </c>
       <c r="P8" t="n">
-        <v>370.5578458293743</v>
+        <v>370.7693761381469</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30173,28 +30500,28 @@
         <v>0.1247</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1060017884986017</v>
+        <v>0.07829639632172082</v>
       </c>
       <c r="J9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03119022318153919</v>
+        <v>0.01640039423381146</v>
       </c>
       <c r="M9" t="n">
-        <v>3.237228610516242</v>
+        <v>3.336708022237803</v>
       </c>
       <c r="N9" t="n">
-        <v>17.95294133306176</v>
+        <v>19.17970225066807</v>
       </c>
       <c r="O9" t="n">
-        <v>4.237091140518666</v>
+        <v>4.379463694411459</v>
       </c>
       <c r="P9" t="n">
-        <v>375.2097766589073</v>
+        <v>375.5142834242648</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30251,28 +30578,28 @@
         <v>0.1072</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1506543111346038</v>
+        <v>0.1374006214990575</v>
       </c>
       <c r="J10" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K10" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04491177093774024</v>
+        <v>0.0380358871188019</v>
       </c>
       <c r="M10" t="n">
-        <v>3.69930716310394</v>
+        <v>3.719718142388928</v>
       </c>
       <c r="N10" t="n">
-        <v>24.82765121933204</v>
+        <v>24.90789178988118</v>
       </c>
       <c r="O10" t="n">
-        <v>4.982735314998383</v>
+        <v>4.990780679400888</v>
       </c>
       <c r="P10" t="n">
-        <v>377.1934778260151</v>
+        <v>377.3393169163045</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30329,28 +30656,28 @@
         <v>0.1173</v>
       </c>
       <c r="I11" t="n">
-        <v>0.115694139245994</v>
+        <v>0.1177439103081021</v>
       </c>
       <c r="J11" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K11" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03364051522168621</v>
+        <v>0.03564627134214515</v>
       </c>
       <c r="M11" t="n">
-        <v>3.582441194670773</v>
+        <v>3.553524488449998</v>
       </c>
       <c r="N11" t="n">
-        <v>19.77825577778892</v>
+        <v>19.56561124713338</v>
       </c>
       <c r="O11" t="n">
-        <v>4.447275095807423</v>
+        <v>4.423303205426164</v>
       </c>
       <c r="P11" t="n">
-        <v>380.3822405961309</v>
+        <v>380.3596869302806</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30407,28 +30734,28 @@
         <v>0.1139</v>
       </c>
       <c r="I12" t="n">
-        <v>0.05984268273149552</v>
+        <v>0.07009097135665872</v>
       </c>
       <c r="J12" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K12" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L12" t="n">
-        <v>0.008747388209289886</v>
+        <v>0.01213923131723182</v>
       </c>
       <c r="M12" t="n">
-        <v>3.51228723164041</v>
+        <v>3.519012121078833</v>
       </c>
       <c r="N12" t="n">
-        <v>20.87455606805098</v>
+        <v>20.85561322370328</v>
       </c>
       <c r="O12" t="n">
-        <v>4.568868138614966</v>
+        <v>4.56679463340572</v>
       </c>
       <c r="P12" t="n">
-        <v>383.5057522319598</v>
+        <v>383.3929833439838</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30485,28 +30812,28 @@
         <v>0.1126</v>
       </c>
       <c r="I13" t="n">
-        <v>0.04976504918724649</v>
+        <v>0.06561675437252756</v>
       </c>
       <c r="J13" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K13" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L13" t="n">
-        <v>0.007980071785626985</v>
+        <v>0.01369967620535062</v>
       </c>
       <c r="M13" t="n">
-        <v>3.175362029345159</v>
+        <v>3.215861449738146</v>
       </c>
       <c r="N13" t="n">
-        <v>15.83622520507796</v>
+        <v>16.17046907613512</v>
       </c>
       <c r="O13" t="n">
-        <v>3.979475493714964</v>
+        <v>4.021252177635111</v>
       </c>
       <c r="P13" t="n">
-        <v>387.6296057568463</v>
+        <v>387.4551717849255</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30563,28 +30890,28 @@
         <v>0.1163</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1266701629177218</v>
+        <v>0.1412475977189139</v>
       </c>
       <c r="J14" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K14" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03869915410710301</v>
+        <v>0.04785489902913742</v>
       </c>
       <c r="M14" t="n">
-        <v>3.559018097422182</v>
+        <v>3.58294493947268</v>
       </c>
       <c r="N14" t="n">
-        <v>20.50197529551713</v>
+        <v>20.70776027971291</v>
       </c>
       <c r="O14" t="n">
-        <v>4.527910698712723</v>
+        <v>4.550578016001145</v>
       </c>
       <c r="P14" t="n">
-        <v>385.1759546834073</v>
+        <v>385.0155416725495</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30641,28 +30968,28 @@
         <v>0.1195</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1866973927157016</v>
+        <v>0.1925923566441873</v>
       </c>
       <c r="J15" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K15" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L15" t="n">
-        <v>0.06384583595130811</v>
+        <v>0.06909608838367287</v>
       </c>
       <c r="M15" t="n">
-        <v>3.671790423500654</v>
+        <v>3.655497292878025</v>
       </c>
       <c r="N15" t="n">
-        <v>26.28938926324448</v>
+        <v>26.06896225364873</v>
       </c>
       <c r="O15" t="n">
-        <v>5.127317940526458</v>
+        <v>5.10577734078257</v>
       </c>
       <c r="P15" t="n">
-        <v>382.4160057558515</v>
+        <v>382.3511296299484</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30719,28 +31046,28 @@
         <v>0.1336</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1297029370124828</v>
+        <v>0.1410823198946633</v>
       </c>
       <c r="J16" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K16" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="L16" t="n">
-        <v>0.05067742236957895</v>
+        <v>0.05989655011418948</v>
       </c>
       <c r="M16" t="n">
-        <v>3.242861514937109</v>
+        <v>3.267096641762554</v>
       </c>
       <c r="N16" t="n">
-        <v>16.18731324665377</v>
+        <v>16.27323149447377</v>
       </c>
       <c r="O16" t="n">
-        <v>4.023346026214222</v>
+        <v>4.034009357261553</v>
       </c>
       <c r="P16" t="n">
-        <v>384.3113843952044</v>
+        <v>384.1858778297488</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30797,28 +31124,28 @@
         <v>0.1213</v>
       </c>
       <c r="I17" t="n">
-        <v>0.08407984537096073</v>
+        <v>0.1040830351116337</v>
       </c>
       <c r="J17" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K17" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02253398591427636</v>
+        <v>0.03328484733152637</v>
       </c>
       <c r="M17" t="n">
-        <v>3.249286303679308</v>
+        <v>3.313858045225159</v>
       </c>
       <c r="N17" t="n">
-        <v>15.74944910020012</v>
+        <v>16.38737239295201</v>
       </c>
       <c r="O17" t="n">
-        <v>3.968557559139104</v>
+        <v>4.04813196338163</v>
       </c>
       <c r="P17" t="n">
-        <v>385.2441746075124</v>
+        <v>385.0235365582595</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30875,28 +31202,28 @@
         <v>0.1036</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1167767484031682</v>
+        <v>0.1357831005059495</v>
       </c>
       <c r="J18" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K18" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="L18" t="n">
-        <v>0.04872848616758385</v>
+        <v>0.06311648743295617</v>
       </c>
       <c r="M18" t="n">
-        <v>2.909399669052534</v>
+        <v>2.963884745006935</v>
       </c>
       <c r="N18" t="n">
-        <v>13.67263562200755</v>
+        <v>14.25383369990943</v>
       </c>
       <c r="O18" t="n">
-        <v>3.697652717874889</v>
+        <v>3.775424969445087</v>
       </c>
       <c r="P18" t="n">
-        <v>382.6516185177492</v>
+        <v>382.4419796046456</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30953,28 +31280,28 @@
         <v>0.1031</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1629949736816378</v>
+        <v>0.1826794557024838</v>
       </c>
       <c r="J19" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K19" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="L19" t="n">
-        <v>0.07971081833752047</v>
+        <v>0.09600728854003227</v>
       </c>
       <c r="M19" t="n">
-        <v>3.050966636576192</v>
+        <v>3.122677738135547</v>
       </c>
       <c r="N19" t="n">
-        <v>15.753366764745</v>
+        <v>16.36581406311246</v>
       </c>
       <c r="O19" t="n">
-        <v>3.969051116418759</v>
+        <v>4.045468336683957</v>
       </c>
       <c r="P19" t="n">
-        <v>381.2377915698238</v>
+        <v>381.0206904445103</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31031,28 +31358,28 @@
         <v>0.1098</v>
       </c>
       <c r="I20" t="n">
-        <v>0.161648420752494</v>
+        <v>0.1747176236269748</v>
       </c>
       <c r="J20" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K20" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L20" t="n">
-        <v>0.07875150672941256</v>
+        <v>0.09105694761223615</v>
       </c>
       <c r="M20" t="n">
-        <v>3.088081777136042</v>
+        <v>3.112956239326875</v>
       </c>
       <c r="N20" t="n">
-        <v>15.72352973563595</v>
+        <v>15.89612503207458</v>
       </c>
       <c r="O20" t="n">
-        <v>3.965290624359827</v>
+        <v>3.9869944860853</v>
       </c>
       <c r="P20" t="n">
-        <v>377.9012052730433</v>
+        <v>377.7573847181415</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31109,28 +31436,28 @@
         <v>0.0916</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1113157289619802</v>
+        <v>0.1216377688674511</v>
       </c>
       <c r="J21" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K21" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03906881807808771</v>
+        <v>0.04680628865232839</v>
       </c>
       <c r="M21" t="n">
-        <v>3.210078186644508</v>
+        <v>3.228572668592795</v>
       </c>
       <c r="N21" t="n">
-        <v>15.67704763894638</v>
+        <v>15.71839174096853</v>
       </c>
       <c r="O21" t="n">
-        <v>3.95942516521608</v>
+        <v>3.964642700290725</v>
       </c>
       <c r="P21" t="n">
-        <v>377.8865514759996</v>
+        <v>377.7729655666934</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -31187,28 +31514,28 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1526457555192546</v>
+        <v>0.1582632744357337</v>
       </c>
       <c r="J22" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K22" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="L22" t="n">
-        <v>0.05793894330481963</v>
+        <v>0.06331164617369744</v>
       </c>
       <c r="M22" t="n">
-        <v>3.513571323348022</v>
+        <v>3.50785440425261</v>
       </c>
       <c r="N22" t="n">
-        <v>19.27261296135371</v>
+        <v>19.11942564110647</v>
       </c>
       <c r="O22" t="n">
-        <v>4.390058423455628</v>
+        <v>4.372576544911075</v>
       </c>
       <c r="P22" t="n">
-        <v>376.8684747098814</v>
+        <v>376.806193734341</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -31265,28 +31592,28 @@
         <v>0.09669999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2629891988466274</v>
+        <v>0.2641528937277283</v>
       </c>
       <c r="J23" t="n">
+        <v>268</v>
+      </c>
+      <c r="K23" t="n">
         <v>265</v>
       </c>
-      <c r="K23" t="n">
-        <v>262</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.1362513974513904</v>
+        <v>0.140327224145863</v>
       </c>
       <c r="M23" t="n">
-        <v>3.829670005611907</v>
+        <v>3.792117575835496</v>
       </c>
       <c r="N23" t="n">
-        <v>22.06931472681757</v>
+        <v>21.822253380509</v>
       </c>
       <c r="O23" t="n">
-        <v>4.69779892362557</v>
+        <v>4.67142947934666</v>
       </c>
       <c r="P23" t="n">
-        <v>374.9899572272698</v>
+        <v>374.9769399579743</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -31343,28 +31670,28 @@
         <v>0.0977</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2977169412487028</v>
+        <v>0.3042119584350113</v>
       </c>
       <c r="J24" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K24" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2127999625476498</v>
+        <v>0.2236649646602292</v>
       </c>
       <c r="M24" t="n">
-        <v>3.238075997805252</v>
+        <v>3.235718443590051</v>
       </c>
       <c r="N24" t="n">
-        <v>16.43063857346266</v>
+        <v>16.32837494151304</v>
       </c>
       <c r="O24" t="n">
-        <v>4.053472409362453</v>
+        <v>4.040838395867007</v>
       </c>
       <c r="P24" t="n">
-        <v>375.0125588376658</v>
+        <v>374.9398762839023</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -31421,28 +31748,28 @@
         <v>0.0916</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3013409415863693</v>
+        <v>0.3111111933576443</v>
       </c>
       <c r="J25" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K25" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1477780233517323</v>
+        <v>0.1584168985096905</v>
       </c>
       <c r="M25" t="n">
-        <v>4.074704415530214</v>
+        <v>4.078204136920086</v>
       </c>
       <c r="N25" t="n">
-        <v>26.24175913397399</v>
+        <v>26.13761451802904</v>
       </c>
       <c r="O25" t="n">
-        <v>5.122671093675055</v>
+        <v>5.112495918632018</v>
       </c>
       <c r="P25" t="n">
-        <v>375.322215425377</v>
+        <v>375.2128912674351</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -31499,28 +31826,28 @@
         <v>0.1013</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1796104657215147</v>
+        <v>0.1836159714616868</v>
       </c>
       <c r="J26" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K26" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="L26" t="n">
-        <v>0.06317299229935103</v>
+        <v>0.06733858124496084</v>
       </c>
       <c r="M26" t="n">
-        <v>3.791377711514524</v>
+        <v>3.769691690721795</v>
       </c>
       <c r="N26" t="n">
-        <v>23.97314536331109</v>
+        <v>23.73668870629675</v>
       </c>
       <c r="O26" t="n">
-        <v>4.896237878546251</v>
+        <v>4.872031271071312</v>
       </c>
       <c r="P26" t="n">
-        <v>373.2953248778956</v>
+        <v>373.2504841912623</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -31577,28 +31904,28 @@
         <v>0.1481</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2593261356658926</v>
+        <v>0.263618805522303</v>
       </c>
       <c r="J27" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K27" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0906100367848508</v>
+        <v>0.09543708288827935</v>
       </c>
       <c r="M27" t="n">
-        <v>4.558696807601475</v>
+        <v>4.525964689588837</v>
       </c>
       <c r="N27" t="n">
-        <v>33.82207231336572</v>
+        <v>33.48216823697685</v>
       </c>
       <c r="O27" t="n">
-        <v>5.815674708352052</v>
+        <v>5.786377816646339</v>
       </c>
       <c r="P27" t="n">
-        <v>372.4246626032506</v>
+        <v>372.3766413126611</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -31655,28 +31982,28 @@
         <v>0.0771</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2507375480075499</v>
+        <v>0.2638591932945415</v>
       </c>
       <c r="J28" t="n">
+        <v>268</v>
+      </c>
+      <c r="K28" t="n">
         <v>265</v>
       </c>
-      <c r="K28" t="n">
-        <v>262</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.06696908460092899</v>
+        <v>0.07482878837753493</v>
       </c>
       <c r="M28" t="n">
-        <v>5.323043689770919</v>
+        <v>5.324458483362161</v>
       </c>
       <c r="N28" t="n">
-        <v>43.55536465399078</v>
+        <v>43.42062030347158</v>
       </c>
       <c r="O28" t="n">
-        <v>6.59964882808099</v>
+        <v>6.589432472032138</v>
       </c>
       <c r="P28" t="n">
-        <v>377.5072830530528</v>
+        <v>377.3596553770369</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -31733,28 +32060,28 @@
         <v>0.123</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2704315215342158</v>
+        <v>0.2751591463785902</v>
       </c>
       <c r="J29" t="n">
+        <v>268</v>
+      </c>
+      <c r="K29" t="n">
         <v>265</v>
       </c>
-      <c r="K29" t="n">
-        <v>262</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.09987594386336862</v>
+        <v>0.1052893808169197</v>
       </c>
       <c r="M29" t="n">
-        <v>4.605414910864929</v>
+        <v>4.573319267650709</v>
       </c>
       <c r="N29" t="n">
-        <v>32.77459462687806</v>
+        <v>32.45369069804348</v>
       </c>
       <c r="O29" t="n">
-        <v>5.724910010373792</v>
+        <v>5.696814083155907</v>
       </c>
       <c r="P29" t="n">
-        <v>388.8361121093129</v>
+        <v>388.7829286515353</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -31815,28 +32142,28 @@
         <v>0.1952</v>
       </c>
       <c r="I30" t="n">
-        <v>0.01651380714336668</v>
+        <v>0.01716248747054356</v>
       </c>
       <c r="J30" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K30" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0002766881150991773</v>
+        <v>0.0003067403706212835</v>
       </c>
       <c r="M30" t="n">
-        <v>5.249928474012561</v>
+        <v>5.193668026011911</v>
       </c>
       <c r="N30" t="n">
-        <v>47.46804280886435</v>
+        <v>46.92835507556967</v>
       </c>
       <c r="O30" t="n">
-        <v>6.889705567646875</v>
+        <v>6.850427364447394</v>
       </c>
       <c r="P30" t="n">
-        <v>397.366757756292</v>
+        <v>397.3593231585806</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -31878,7 +32205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE266"/>
+  <dimension ref="A1:AE269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73405,7 +73732,7 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>-35.69949363160011,174.5159552081647</t>
+          <t>-35.69950655665671,174.5159079539072</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -73514,6 +73841,477 @@
         </is>
       </c>
       <c r="AE266" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>-35.694536691949935,174.51478768452688</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>-35.695261481120184,174.51488976727154</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>-35.69599290893493,174.51477672071164</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>-35.696716584715205,174.51486481416873</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>-35.6974289583914,174.5150663180719</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>-35.69812913431564,174.51531850158722</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>-35.6988205208525,174.51560574290627</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>-35.69951142862455,174.515890141877</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>-35.70017639575886,174.51626580052155</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>-35.70083868302967,174.51665333455128</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>-35.70151173694175,174.51700357592648</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>-35.7021762016671,174.51735496462214</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>-35.7028502911224,174.51766946746895</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>-35.70354221990263,174.51795760701162</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>-35.7042045456204,174.51832395633153</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>-35.704846261400306,174.51871836375227</t>
+        </is>
+      </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>-35.705493099297684,174.519102048585</t>
+        </is>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>-35.7061216944813,174.51953083610178</t>
+        </is>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>-35.706772719802764,174.5199261045077</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>-35.70740612718164,174.52037273840253</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>-35.70803828718613,174.52082037811383</t>
+        </is>
+      </c>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>-35.70866374252377,174.52128101106146</t>
+        </is>
+      </c>
+      <c r="X267" t="inlineStr">
+        <is>
+          <t>-35.709265503308295,174.52178585072392</t>
+        </is>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>-35.70985852258677,174.52228276864645</t>
+        </is>
+      </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>-35.71047883424655,174.52274401372526</t>
+        </is>
+      </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>-35.7110412912355,174.52331624189765</t>
+        </is>
+      </c>
+      <c r="AB267" t="inlineStr">
+        <is>
+          <t>-35.71156473993457,174.5239470408736</t>
+        </is>
+      </c>
+      <c r="AC267" t="inlineStr">
+        <is>
+          <t>-35.712094610998875,174.5245633476447</t>
+        </is>
+      </c>
+      <c r="AD267" t="inlineStr">
+        <is>
+          <t>-35.712668798685264,174.52511430362355</t>
+        </is>
+      </c>
+      <c r="AE267" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>-35.69453656151274,174.51478911214588</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>-35.69525921349908,174.51491458609925</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>-35.69599252546027,174.51477910594966</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>-35.696718663141446,174.51485611822739</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>-35.69742898436571,174.51506621225138</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>-35.69812853690292,174.5153209354787</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>-35.69882030808016,174.5156065876246</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>-35.699511170696894,174.5158910848669</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>-35.70017552309933,174.51626882150683</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>-35.700838141374334,174.5166552096588</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>-35.70151378321034,174.5169964921346</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>-35.702177266331155,174.51735155924175</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>-35.70284612614022,174.51768170679895</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>-35.703537704399274,174.51797074479364</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>-35.70419891380269,174.51833975391833</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>-35.70484452216895,174.51872273407136</t>
+        </is>
+      </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>-35.70549224411985,174.51910399445904</t>
+        </is>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>-35.70612310807166,174.5195278806951</t>
+        </is>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>-35.706769110760895,174.51993324401624</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>-35.70740674452063,174.52037151716357</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>-35.70803962385215,174.5208177530813</t>
+        </is>
+      </c>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>-35.7086635982979,174.52128129153888</t>
+        </is>
+      </c>
+      <c r="X268" t="inlineStr">
+        <is>
+          <t>-35.709266866172484,174.52178324598168</t>
+        </is>
+      </c>
+      <c r="Y268" t="inlineStr">
+        <is>
+          <t>-35.70986361195438,174.52227405095098</t>
+        </is>
+      </c>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t>-35.71047633004398,174.5227479264569</t>
+        </is>
+      </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>-35.71104657791077,174.5233079816552</t>
+        </is>
+      </c>
+      <c r="AB268" t="inlineStr">
+        <is>
+          <t>-35.711577556659186,174.52392719983706</t>
+        </is>
+      </c>
+      <c r="AC268" t="inlineStr">
+        <is>
+          <t>-35.712102369830305,174.524551567023</t>
+        </is>
+      </c>
+      <c r="AD268" t="inlineStr">
+        <is>
+          <t>-35.71266629154948,174.5251180720314</t>
+        </is>
+      </c>
+      <c r="AE268" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>-35.69453577888928,174.51479767785972</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>-35.695257136514236,174.51493731838698</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>-35.69599160163475,174.51478485220477</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>-35.69672008255412,174.51485017953547</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>-35.697428672674015,174.51506748209752</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>-35.69812952393261,174.51531691426663</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>-35.698822116644855,174.51559940751883</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>-35.69950827617507,174.51590166730858</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>-35.700174590256324,174.51627205083585</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>-35.70083913440911,174.51665177196165</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>-35.701513331827606,174.5169980547358</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>-35.70217662108022,174.51735362310865</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>-35.702849319293335,174.51767232331272</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>-35.70353938458673,174.5179658563168</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>-35.70420162140761,174.51833215892498</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>-35.704842506241505,174.51872779966823</t>
+        </is>
+      </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>-35.70549074755856,174.51910739973852</t>
+        </is>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>-35.706125752853424,174.51952235122423</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>-35.70677015548358,174.51993117731647</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>-35.707406079694024,174.52037283234398</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>-35.70803852587649,174.52081990935804</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>-35.70866258871677,174.52128325488073</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>-35.70926769362572,174.52178166453103</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>-35.70986670754881,174.5222687484346</t>
+        </is>
+      </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>-35.71047232331965,174.52275418682706</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>-35.71105058465378,174.52330172126017</t>
+        </is>
+      </c>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>-35.71158444075016,174.52391654285847</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>-35.71210480508372,174.52454786945512</t>
+        </is>
+      </c>
+      <c r="AD269" t="inlineStr">
+        <is>
+          <t>-35.712670394135245,174.5251119055457</t>
+        </is>
+      </c>
+      <c r="AE269" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0097/nzd0097.xlsx
+++ b/data/nzd0097/nzd0097.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE269"/>
+  <dimension ref="A1:AE272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27053,6 +27053,303 @@
         <v>397.74</v>
       </c>
       <c r="AE269" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>397.13</v>
+      </c>
+      <c r="C270" t="n">
+        <v>402.69</v>
+      </c>
+      <c r="D270" t="n">
+        <v>381.98</v>
+      </c>
+      <c r="E270" t="n">
+        <v>364.84</v>
+      </c>
+      <c r="F270" t="n">
+        <v>361.77</v>
+      </c>
+      <c r="G270" t="n">
+        <v>361.56</v>
+      </c>
+      <c r="H270" t="n">
+        <v>364.59</v>
+      </c>
+      <c r="I270" t="n">
+        <v>369.58</v>
+      </c>
+      <c r="J270" t="n">
+        <v>375.99</v>
+      </c>
+      <c r="K270" t="n">
+        <v>384.21</v>
+      </c>
+      <c r="L270" t="n">
+        <v>389.44</v>
+      </c>
+      <c r="M270" t="n">
+        <v>395.93</v>
+      </c>
+      <c r="N270" t="n">
+        <v>393.75</v>
+      </c>
+      <c r="O270" t="n">
+        <v>390.09</v>
+      </c>
+      <c r="P270" t="n">
+        <v>392.73</v>
+      </c>
+      <c r="Q270" t="n">
+        <v>396.31</v>
+      </c>
+      <c r="R270" t="n">
+        <v>393.89</v>
+      </c>
+      <c r="S270" t="n">
+        <v>393.1</v>
+      </c>
+      <c r="T270" t="n">
+        <v>387.2</v>
+      </c>
+      <c r="U270" t="n">
+        <v>385.61</v>
+      </c>
+      <c r="V270" t="n">
+        <v>383.82</v>
+      </c>
+      <c r="W270" t="n">
+        <v>383.19</v>
+      </c>
+      <c r="X270" t="n">
+        <v>385.44</v>
+      </c>
+      <c r="Y270" t="n">
+        <v>386.85</v>
+      </c>
+      <c r="Z270" t="n">
+        <v>381.3</v>
+      </c>
+      <c r="AA270" t="n">
+        <v>382.05</v>
+      </c>
+      <c r="AB270" t="n">
+        <v>389.38</v>
+      </c>
+      <c r="AC270" t="n">
+        <v>397.89</v>
+      </c>
+      <c r="AD270" t="n">
+        <v>397.98</v>
+      </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>395.25</v>
+      </c>
+      <c r="C271" t="n">
+        <v>402.1</v>
+      </c>
+      <c r="D271" t="n">
+        <v>380.15</v>
+      </c>
+      <c r="E271" t="n">
+        <v>362.59</v>
+      </c>
+      <c r="F271" t="n">
+        <v>360.01</v>
+      </c>
+      <c r="G271" t="n">
+        <v>359.87</v>
+      </c>
+      <c r="H271" t="n">
+        <v>362.11</v>
+      </c>
+      <c r="I271" t="n">
+        <v>367.67</v>
+      </c>
+      <c r="J271" t="n">
+        <v>373.99</v>
+      </c>
+      <c r="K271" t="n">
+        <v>381.61</v>
+      </c>
+      <c r="L271" t="n">
+        <v>387.8</v>
+      </c>
+      <c r="M271" t="n">
+        <v>393.97</v>
+      </c>
+      <c r="N271" t="n">
+        <v>391.69</v>
+      </c>
+      <c r="O271" t="n">
+        <v>388.12</v>
+      </c>
+      <c r="P271" t="n">
+        <v>391.76</v>
+      </c>
+      <c r="Q271" t="n">
+        <v>394.86</v>
+      </c>
+      <c r="R271" t="n">
+        <v>392.39</v>
+      </c>
+      <c r="S271" t="n">
+        <v>390.65</v>
+      </c>
+      <c r="T271" t="n">
+        <v>385.31</v>
+      </c>
+      <c r="U271" t="n">
+        <v>383.68</v>
+      </c>
+      <c r="V271" t="n">
+        <v>382.6</v>
+      </c>
+      <c r="W271" t="n">
+        <v>381.36</v>
+      </c>
+      <c r="X271" t="n">
+        <v>383.37</v>
+      </c>
+      <c r="Y271" t="n">
+        <v>386.09</v>
+      </c>
+      <c r="Z271" t="n">
+        <v>380.51</v>
+      </c>
+      <c r="AA271" t="n">
+        <v>381.31</v>
+      </c>
+      <c r="AB271" t="n">
+        <v>388.13</v>
+      </c>
+      <c r="AC271" t="n">
+        <v>395.35</v>
+      </c>
+      <c r="AD271" t="n">
+        <v>396.13</v>
+      </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>394.49</v>
+      </c>
+      <c r="C272" t="n">
+        <v>403.38</v>
+      </c>
+      <c r="D272" t="n">
+        <v>381.86</v>
+      </c>
+      <c r="E272" t="n">
+        <v>362.72</v>
+      </c>
+      <c r="F272" t="n">
+        <v>359.36</v>
+      </c>
+      <c r="G272" t="n">
+        <v>360.06</v>
+      </c>
+      <c r="H272" t="n">
+        <v>362.16</v>
+      </c>
+      <c r="I272" t="n">
+        <v>367.61</v>
+      </c>
+      <c r="J272" t="n">
+        <v>373.49</v>
+      </c>
+      <c r="K272" t="n">
+        <v>381.87</v>
+      </c>
+      <c r="L272" t="n">
+        <v>387.26</v>
+      </c>
+      <c r="M272" t="n">
+        <v>393.95</v>
+      </c>
+      <c r="N272" t="n">
+        <v>391.34</v>
+      </c>
+      <c r="O272" t="n">
+        <v>387.34</v>
+      </c>
+      <c r="P272" t="n">
+        <v>391.32</v>
+      </c>
+      <c r="Q272" t="n">
+        <v>394.61</v>
+      </c>
+      <c r="R272" t="n">
+        <v>392.84</v>
+      </c>
+      <c r="S272" t="n">
+        <v>389.92</v>
+      </c>
+      <c r="T272" t="n">
+        <v>384.83</v>
+      </c>
+      <c r="U272" t="n">
+        <v>382.67</v>
+      </c>
+      <c r="V272" t="n">
+        <v>382.1</v>
+      </c>
+      <c r="W272" t="n">
+        <v>379.87</v>
+      </c>
+      <c r="X272" t="n">
+        <v>380.81</v>
+      </c>
+      <c r="Y272" t="n">
+        <v>384.88</v>
+      </c>
+      <c r="Z272" t="n">
+        <v>381.57</v>
+      </c>
+      <c r="AA272" t="n">
+        <v>383.12</v>
+      </c>
+      <c r="AB272" t="n">
+        <v>390.21</v>
+      </c>
+      <c r="AC272" t="n">
+        <v>395.4</v>
+      </c>
+      <c r="AD272" t="n">
+        <v>396.09</v>
+      </c>
+      <c r="AE272" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27069,7 +27366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B271"/>
+  <dimension ref="A1:B274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29782,6 +30079,36 @@
       </c>
       <c r="B271" t="n">
         <v>-0.63</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>-0.12</v>
       </c>
     </row>
   </sheetData>
@@ -29950,28 +30277,28 @@
         <v>0.0566</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08550680932018381</v>
+        <v>0.09242281592422301</v>
       </c>
       <c r="J2" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K2" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L2" t="n">
-        <v>0.009782620629213867</v>
+        <v>0.01165576415674974</v>
       </c>
       <c r="M2" t="n">
-        <v>4.407328154226184</v>
+        <v>4.391500764821195</v>
       </c>
       <c r="N2" t="n">
-        <v>38.55063311629959</v>
+        <v>38.23776768012307</v>
       </c>
       <c r="O2" t="n">
-        <v>6.208915615169817</v>
+        <v>6.183669434900533</v>
       </c>
       <c r="P2" t="n">
-        <v>390.2581352827073</v>
+        <v>390.1815960223092</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30032,28 +30359,28 @@
         <v>0.0609</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02883222267367242</v>
+        <v>-0.02307030915467282</v>
       </c>
       <c r="J3" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K3" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001410955985712947</v>
+        <v>0.0009240180259971753</v>
       </c>
       <c r="M3" t="n">
-        <v>4.387878405627534</v>
+        <v>4.368124393904278</v>
       </c>
       <c r="N3" t="n">
-        <v>30.59596411479209</v>
+        <v>30.32817151253147</v>
       </c>
       <c r="O3" t="n">
-        <v>5.531361868002499</v>
+        <v>5.507101915938316</v>
       </c>
       <c r="P3" t="n">
-        <v>400.9355218208671</v>
+        <v>400.8715735222938</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30110,28 +30437,28 @@
         <v>0.132</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.005666645589536958</v>
+        <v>-0.008640535467318614</v>
       </c>
       <c r="J4" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K4" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L4" t="n">
-        <v>9.025253535510647e-05</v>
+        <v>0.0002147200135456107</v>
       </c>
       <c r="M4" t="n">
-        <v>3.379793241491447</v>
+        <v>3.357646559764339</v>
       </c>
       <c r="N4" t="n">
-        <v>18.52895660092232</v>
+        <v>18.34955267915418</v>
       </c>
       <c r="O4" t="n">
-        <v>4.304527453846975</v>
+        <v>4.283637785709033</v>
       </c>
       <c r="P4" t="n">
-        <v>382.8029160054835</v>
+        <v>382.8358498678422</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30188,28 +30515,28 @@
         <v>0.1347</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08519947136003031</v>
+        <v>0.0771029545521822</v>
       </c>
       <c r="J5" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K5" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01777724077871545</v>
+        <v>0.01485717901996941</v>
       </c>
       <c r="M5" t="n">
-        <v>3.519382122513637</v>
+        <v>3.52004006927364</v>
       </c>
       <c r="N5" t="n">
-        <v>20.92250565386299</v>
+        <v>20.84186904285579</v>
       </c>
       <c r="O5" t="n">
-        <v>4.574112553694213</v>
+        <v>4.56528959025118</v>
       </c>
       <c r="P5" t="n">
-        <v>364.7194795919801</v>
+        <v>364.8089470886424</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30266,28 +30593,28 @@
         <v>0.114</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2247174697650185</v>
+        <v>0.2127428033994812</v>
       </c>
       <c r="J6" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K6" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09620543710860296</v>
+        <v>0.08803266847502378</v>
       </c>
       <c r="M6" t="n">
-        <v>3.849319075841921</v>
+        <v>3.87194668460109</v>
       </c>
       <c r="N6" t="n">
-        <v>24.74788190749372</v>
+        <v>24.79002427152783</v>
       </c>
       <c r="O6" t="n">
-        <v>4.97472430467194</v>
+        <v>4.978958151212744</v>
       </c>
       <c r="P6" t="n">
-        <v>359.7184748228167</v>
+        <v>359.8507852283261</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30344,28 +30671,28 @@
         <v>0.1066</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1909677314717765</v>
+        <v>0.1717025652223086</v>
       </c>
       <c r="J7" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K7" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08557059547169599</v>
+        <v>0.06940643767764687</v>
       </c>
       <c r="M7" t="n">
-        <v>3.54127468112407</v>
+        <v>3.604407865999162</v>
       </c>
       <c r="N7" t="n">
-        <v>20.33011625860507</v>
+        <v>20.89996880439502</v>
       </c>
       <c r="O7" t="n">
-        <v>4.508893019201617</v>
+        <v>4.571648368411007</v>
       </c>
       <c r="P7" t="n">
-        <v>363.9917317766481</v>
+        <v>364.2045693894314</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30422,28 +30749,28 @@
         <v>0.1191</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07914972121313101</v>
+        <v>0.05688274391350828</v>
       </c>
       <c r="J8" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K8" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01570934285411318</v>
+        <v>0.007961155400789011</v>
       </c>
       <c r="M8" t="n">
-        <v>3.499918935406412</v>
+        <v>3.582150944905517</v>
       </c>
       <c r="N8" t="n">
-        <v>20.47662509618243</v>
+        <v>21.31794971933374</v>
       </c>
       <c r="O8" t="n">
-        <v>4.525110506516103</v>
+        <v>4.617136528123654</v>
       </c>
       <c r="P8" t="n">
-        <v>370.7693761381469</v>
+        <v>371.0153852081907</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30500,28 +30827,28 @@
         <v>0.1247</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07829639632172082</v>
+        <v>0.05739714145880477</v>
       </c>
       <c r="J9" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K9" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01640039423381146</v>
+        <v>0.0086751460150013</v>
       </c>
       <c r="M9" t="n">
-        <v>3.336708022237803</v>
+        <v>3.408213760916499</v>
       </c>
       <c r="N9" t="n">
-        <v>19.17970225066807</v>
+        <v>19.90451090903004</v>
       </c>
       <c r="O9" t="n">
-        <v>4.379463694411459</v>
+        <v>4.461447176537008</v>
       </c>
       <c r="P9" t="n">
-        <v>375.5142834242648</v>
+        <v>375.7451775336135</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30578,28 +30905,28 @@
         <v>0.1072</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1374006214990575</v>
+        <v>0.1227855026362206</v>
       </c>
       <c r="J10" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K10" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0380358871188019</v>
+        <v>0.03078184903550929</v>
       </c>
       <c r="M10" t="n">
-        <v>3.719718142388928</v>
+        <v>3.750143485257374</v>
       </c>
       <c r="N10" t="n">
-        <v>24.90789178988118</v>
+        <v>25.09879094345066</v>
       </c>
       <c r="O10" t="n">
-        <v>4.990780679400888</v>
+        <v>5.009869353930365</v>
       </c>
       <c r="P10" t="n">
-        <v>377.3393169163045</v>
+        <v>377.5007972504483</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30656,28 +30983,28 @@
         <v>0.1173</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1177439103081021</v>
+        <v>0.1156303541337854</v>
       </c>
       <c r="J11" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K11" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03564627134214515</v>
+        <v>0.0352045064137958</v>
       </c>
       <c r="M11" t="n">
-        <v>3.553524488449998</v>
+        <v>3.528485143074616</v>
       </c>
       <c r="N11" t="n">
-        <v>19.56561124713338</v>
+        <v>19.37369684146147</v>
       </c>
       <c r="O11" t="n">
-        <v>4.423303205426164</v>
+        <v>4.401556184062799</v>
       </c>
       <c r="P11" t="n">
-        <v>380.3596869302806</v>
+        <v>380.3830651644311</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30734,28 +31061,28 @@
         <v>0.1139</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07009097135665872</v>
+        <v>0.07659525377861076</v>
       </c>
       <c r="J12" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K12" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01213923131723182</v>
+        <v>0.01474697507345479</v>
       </c>
       <c r="M12" t="n">
-        <v>3.519012121078833</v>
+        <v>3.509881532287456</v>
       </c>
       <c r="N12" t="n">
-        <v>20.85561322370328</v>
+        <v>20.72432198666628</v>
       </c>
       <c r="O12" t="n">
-        <v>4.56679463340572</v>
+        <v>4.552397388922267</v>
       </c>
       <c r="P12" t="n">
-        <v>383.3929833439838</v>
+        <v>383.3211580483398</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30812,28 +31139,28 @@
         <v>0.1126</v>
       </c>
       <c r="I13" t="n">
-        <v>0.06561675437252756</v>
+        <v>0.07774456131508659</v>
       </c>
       <c r="J13" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K13" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01369967620535062</v>
+        <v>0.0192126665904101</v>
       </c>
       <c r="M13" t="n">
-        <v>3.215861449738146</v>
+        <v>3.239979758182481</v>
       </c>
       <c r="N13" t="n">
-        <v>16.17046907613512</v>
+        <v>16.31394592371568</v>
       </c>
       <c r="O13" t="n">
-        <v>4.021252177635111</v>
+        <v>4.039052602246681</v>
       </c>
       <c r="P13" t="n">
-        <v>387.4551717849255</v>
+        <v>387.3212235493842</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30890,28 +31217,28 @@
         <v>0.1163</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1412475977189139</v>
+        <v>0.1490314878579754</v>
       </c>
       <c r="J14" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K14" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04785489902913742</v>
+        <v>0.0538818322732707</v>
       </c>
       <c r="M14" t="n">
-        <v>3.58294493947268</v>
+        <v>3.577463578743078</v>
       </c>
       <c r="N14" t="n">
-        <v>20.70776027971291</v>
+        <v>20.62010547635858</v>
       </c>
       <c r="O14" t="n">
-        <v>4.550578016001145</v>
+        <v>4.540936629854967</v>
       </c>
       <c r="P14" t="n">
-        <v>385.0155416725495</v>
+        <v>384.9295842890123</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30968,28 +31295,28 @@
         <v>0.1195</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1925923566441873</v>
+        <v>0.1948776102743014</v>
       </c>
       <c r="J15" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K15" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L15" t="n">
-        <v>0.06909608838367287</v>
+        <v>0.07219116015500382</v>
       </c>
       <c r="M15" t="n">
-        <v>3.655497292878025</v>
+        <v>3.626053106630351</v>
       </c>
       <c r="N15" t="n">
-        <v>26.06896225364873</v>
+        <v>25.80656236837351</v>
       </c>
       <c r="O15" t="n">
-        <v>5.10577734078257</v>
+        <v>5.080015981113988</v>
       </c>
       <c r="P15" t="n">
-        <v>382.3511296299484</v>
+        <v>382.325917785415</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31046,28 +31373,28 @@
         <v>0.1336</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1410823198946633</v>
+        <v>0.150026213368536</v>
       </c>
       <c r="J16" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K16" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L16" t="n">
-        <v>0.05989655011418948</v>
+        <v>0.06807572681786422</v>
       </c>
       <c r="M16" t="n">
-        <v>3.267096641762554</v>
+        <v>3.280799178530793</v>
       </c>
       <c r="N16" t="n">
-        <v>16.27323149447377</v>
+        <v>16.26631909733311</v>
       </c>
       <c r="O16" t="n">
-        <v>4.034009357261553</v>
+        <v>4.033152501125281</v>
       </c>
       <c r="P16" t="n">
-        <v>384.1858778297488</v>
+        <v>384.0868720409023</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31124,28 +31451,28 @@
         <v>0.1213</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1040830351116337</v>
+        <v>0.1208354825083822</v>
       </c>
       <c r="J17" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K17" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03328484733152637</v>
+        <v>0.04384486745454719</v>
       </c>
       <c r="M17" t="n">
-        <v>3.313858045225159</v>
+        <v>3.361556027016986</v>
       </c>
       <c r="N17" t="n">
-        <v>16.38737239295201</v>
+        <v>16.80770879803525</v>
       </c>
       <c r="O17" t="n">
-        <v>4.04813196338163</v>
+        <v>4.099720575604543</v>
       </c>
       <c r="P17" t="n">
-        <v>385.0235365582595</v>
+        <v>384.8380678073815</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31202,28 +31529,28 @@
         <v>0.1036</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1357831005059495</v>
+        <v>0.1514554146880447</v>
       </c>
       <c r="J18" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K18" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L18" t="n">
-        <v>0.06311648743295617</v>
+        <v>0.07647744686305502</v>
       </c>
       <c r="M18" t="n">
-        <v>2.963884745006935</v>
+        <v>3.005332073521294</v>
       </c>
       <c r="N18" t="n">
-        <v>14.25383369990943</v>
+        <v>14.62155924809592</v>
       </c>
       <c r="O18" t="n">
-        <v>3.775424969445087</v>
+        <v>3.823814750755575</v>
       </c>
       <c r="P18" t="n">
-        <v>382.4419796046456</v>
+        <v>382.2684640989793</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -31280,28 +31607,28 @@
         <v>0.1031</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1826794557024838</v>
+        <v>0.194638107533169</v>
       </c>
       <c r="J19" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K19" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L19" t="n">
-        <v>0.09600728854003227</v>
+        <v>0.1080430279917212</v>
       </c>
       <c r="M19" t="n">
-        <v>3.122677738135547</v>
+        <v>3.154388839940935</v>
       </c>
       <c r="N19" t="n">
-        <v>16.36581406311246</v>
+        <v>16.50869936394008</v>
       </c>
       <c r="O19" t="n">
-        <v>4.045468336683957</v>
+        <v>4.063089878890212</v>
       </c>
       <c r="P19" t="n">
-        <v>381.0206904445103</v>
+        <v>380.8883181111061</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31358,28 +31685,28 @@
         <v>0.1098</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1747176236269748</v>
+        <v>0.1822441533453132</v>
       </c>
       <c r="J20" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K20" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L20" t="n">
-        <v>0.09105694761223615</v>
+        <v>0.09972825676130148</v>
       </c>
       <c r="M20" t="n">
-        <v>3.112956239326875</v>
+        <v>3.112481270086053</v>
       </c>
       <c r="N20" t="n">
-        <v>15.89612503207458</v>
+        <v>15.85237662603435</v>
       </c>
       <c r="O20" t="n">
-        <v>3.9869944860853</v>
+        <v>3.981504316967941</v>
       </c>
       <c r="P20" t="n">
-        <v>377.7573847181415</v>
+        <v>377.6742694759219</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31436,28 +31763,28 @@
         <v>0.0916</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1216377688674511</v>
+        <v>0.1282840763560777</v>
       </c>
       <c r="J21" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K21" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L21" t="n">
-        <v>0.04680628865232839</v>
+        <v>0.05265394669876755</v>
       </c>
       <c r="M21" t="n">
-        <v>3.228572668592795</v>
+        <v>3.227646118036031</v>
       </c>
       <c r="N21" t="n">
-        <v>15.71839174096853</v>
+        <v>15.65506969825101</v>
       </c>
       <c r="O21" t="n">
-        <v>3.964642700290725</v>
+        <v>3.956648796424951</v>
       </c>
       <c r="P21" t="n">
-        <v>377.7729655666934</v>
+        <v>377.6995798546254</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -31514,28 +31841,28 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1582632744357337</v>
+        <v>0.1623501649458715</v>
       </c>
       <c r="J22" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K22" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L22" t="n">
-        <v>0.06331164617369744</v>
+        <v>0.06781428516184085</v>
       </c>
       <c r="M22" t="n">
-        <v>3.50785440425261</v>
+        <v>3.493161616684661</v>
       </c>
       <c r="N22" t="n">
-        <v>19.11942564110647</v>
+        <v>18.94786093652776</v>
       </c>
       <c r="O22" t="n">
-        <v>4.372576544911075</v>
+        <v>4.352914074103434</v>
       </c>
       <c r="P22" t="n">
-        <v>376.806193734341</v>
+        <v>376.7607293830956</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -31592,28 +31919,28 @@
         <v>0.09669999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2641528937277283</v>
+        <v>0.2628741685936692</v>
       </c>
       <c r="J23" t="n">
+        <v>271</v>
+      </c>
+      <c r="K23" t="n">
         <v>268</v>
       </c>
-      <c r="K23" t="n">
-        <v>265</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.140327224145863</v>
+        <v>0.1420157004207366</v>
       </c>
       <c r="M23" t="n">
-        <v>3.792117575835496</v>
+        <v>3.764304033518073</v>
       </c>
       <c r="N23" t="n">
-        <v>21.822253380509</v>
+        <v>21.60212435419843</v>
       </c>
       <c r="O23" t="n">
-        <v>4.67142947934666</v>
+        <v>4.647808553952974</v>
       </c>
       <c r="P23" t="n">
-        <v>374.9769399579743</v>
+        <v>374.9913347508927</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -31670,28 +31997,28 @@
         <v>0.0977</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3042119584350113</v>
+        <v>0.3045345392042351</v>
       </c>
       <c r="J24" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K24" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2236649646602292</v>
+        <v>0.2279436346321609</v>
       </c>
       <c r="M24" t="n">
-        <v>3.235718443590051</v>
+        <v>3.218206666574432</v>
       </c>
       <c r="N24" t="n">
-        <v>16.32837494151304</v>
+        <v>16.18696241443465</v>
       </c>
       <c r="O24" t="n">
-        <v>4.040838395867007</v>
+        <v>4.023302426419701</v>
       </c>
       <c r="P24" t="n">
-        <v>374.9398762839023</v>
+        <v>374.9363055814188</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -31748,28 +32075,28 @@
         <v>0.0916</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3111111933576443</v>
+        <v>0.3166561671079137</v>
       </c>
       <c r="J25" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K25" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1584168985096905</v>
+        <v>0.1662313818597984</v>
       </c>
       <c r="M25" t="n">
-        <v>4.078204136920086</v>
+        <v>4.061054931192636</v>
       </c>
       <c r="N25" t="n">
-        <v>26.13761451802904</v>
+        <v>25.91666640577956</v>
       </c>
       <c r="O25" t="n">
-        <v>5.112495918632018</v>
+        <v>5.090841424143906</v>
       </c>
       <c r="P25" t="n">
-        <v>375.2128912674351</v>
+        <v>375.150622992793</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -31826,28 +32153,28 @@
         <v>0.1013</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1836159714616868</v>
+        <v>0.1904423301573406</v>
       </c>
       <c r="J26" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K26" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="L26" t="n">
-        <v>0.06733858124496084</v>
+        <v>0.07346936424560235</v>
       </c>
       <c r="M26" t="n">
-        <v>3.769691690721795</v>
+        <v>3.76289742780847</v>
       </c>
       <c r="N26" t="n">
-        <v>23.73668870629675</v>
+        <v>23.56954414288072</v>
       </c>
       <c r="O26" t="n">
-        <v>4.872031271071312</v>
+        <v>4.854847489147391</v>
       </c>
       <c r="P26" t="n">
-        <v>373.2504841912623</v>
+        <v>373.1737981354222</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -31904,28 +32231,28 @@
         <v>0.1481</v>
       </c>
       <c r="I27" t="n">
-        <v>0.263618805522303</v>
+        <v>0.2699246775004416</v>
       </c>
       <c r="J27" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K27" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="L27" t="n">
-        <v>0.09543708288827935</v>
+        <v>0.1016091761470018</v>
       </c>
       <c r="M27" t="n">
-        <v>4.525964689588837</v>
+        <v>4.50258477103045</v>
       </c>
       <c r="N27" t="n">
-        <v>33.48216823697685</v>
+        <v>33.19619195453138</v>
       </c>
       <c r="O27" t="n">
-        <v>5.786377816646339</v>
+        <v>5.761613658909401</v>
       </c>
       <c r="P27" t="n">
-        <v>372.3766413126611</v>
+        <v>372.3057940126822</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -31982,28 +32309,28 @@
         <v>0.0771</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2638591932945415</v>
+        <v>0.275033525731823</v>
       </c>
       <c r="J28" t="n">
+        <v>271</v>
+      </c>
+      <c r="K28" t="n">
         <v>268</v>
       </c>
-      <c r="K28" t="n">
-        <v>265</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.07482878837753493</v>
+        <v>0.08219107353952282</v>
       </c>
       <c r="M28" t="n">
-        <v>5.324458483362161</v>
+        <v>5.316772936871457</v>
       </c>
       <c r="N28" t="n">
-        <v>43.42062030347158</v>
+        <v>43.19553485857833</v>
       </c>
       <c r="O28" t="n">
-        <v>6.589432472032138</v>
+        <v>6.572331006467822</v>
       </c>
       <c r="P28" t="n">
-        <v>377.3596553770369</v>
+        <v>377.2334226640102</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -32060,28 +32387,28 @@
         <v>0.123</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2751591463785902</v>
+        <v>0.2753546747735345</v>
       </c>
       <c r="J29" t="n">
+        <v>271</v>
+      </c>
+      <c r="K29" t="n">
         <v>268</v>
       </c>
-      <c r="K29" t="n">
-        <v>265</v>
-      </c>
       <c r="L29" t="n">
-        <v>0.1052893808169197</v>
+        <v>0.1077506932751952</v>
       </c>
       <c r="M29" t="n">
-        <v>4.573319267650709</v>
+        <v>4.534284727156464</v>
       </c>
       <c r="N29" t="n">
-        <v>32.45369069804348</v>
+        <v>32.10635573958326</v>
       </c>
       <c r="O29" t="n">
-        <v>5.696814083155907</v>
+        <v>5.666247059525666</v>
       </c>
       <c r="P29" t="n">
-        <v>388.7829286515353</v>
+        <v>388.7807523695428</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -32142,28 +32469,28 @@
         <v>0.1952</v>
       </c>
       <c r="I30" t="n">
-        <v>0.01716248747054356</v>
+        <v>0.01458570370277839</v>
       </c>
       <c r="J30" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K30" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0003067403706212835</v>
+        <v>0.0002271442153989334</v>
       </c>
       <c r="M30" t="n">
-        <v>5.193668026011911</v>
+        <v>5.147998264609827</v>
       </c>
       <c r="N30" t="n">
-        <v>46.92835507556967</v>
+        <v>46.42063745185784</v>
       </c>
       <c r="O30" t="n">
-        <v>6.850427364447394</v>
+        <v>6.813269219094299</v>
       </c>
       <c r="P30" t="n">
-        <v>397.3593231585806</v>
+        <v>397.3890083345248</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -32205,7 +32532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE269"/>
+  <dimension ref="A1:AE272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74317,6 +74644,477 @@
         </is>
       </c>
     </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>-35.69453663174816,174.51478834342794</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>-35.695256835501574,174.51494061292132</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>-35.69598895217139,174.51480133202998</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>-35.696719550274395,174.51485240654495</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>-35.69742794539334,174.51507044507187</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>-35.69812905639225,174.51531881905132</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>-35.698821611310635,174.51560141372488</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>-35.69950423530643,174.51591644081495</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>-35.70017386805523,174.51627455096153</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>-35.700839074225186,174.51665198030693</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>-35.70151327164323,174.51699826308263</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>-35.7021763952424,174.51735434546205</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>-35.70285247773756,174.51766304182019</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>-35.70353924457111,174.51796626368989</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>-35.70420154920481,174.51833236145814</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>-35.70484377113718,174.51872462125453</t>
+        </is>
+      </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>-35.70549245791431,174.51910350799054</t>
+        </is>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>-35.70612807843718,174.51951748910295</t>
+        </is>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>-35.7067738595001,174.51992384992593</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>-35.70740498747886,174.5203749929975</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>-35.70803652087737,174.52082384690667</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>-35.70865989650027,174.52128849045874</t>
+        </is>
+      </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>-35.7092678883206,174.52178129242495</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>-35.709866287807216,174.52226946741987</t>
+        </is>
+      </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>-35.71046731491378,174.52276201228884</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>-35.71104112428785,174.5233165027474</t>
+        </is>
+      </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>-35.71157744472274,174.52392737312124</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>-35.71210135042185,174.52455311484204</t>
+        </is>
+      </c>
+      <c r="AD270" t="inlineStr">
+        <is>
+          <t>-35.71266902660669,174.525113961041</t>
+        </is>
+      </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>-35.69453851806877,174.51476769786038</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>-35.69525742749305,174.5149341336704</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>-35.695992141985556,174.51478149118765</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>-35.69672525326933,174.5148285457273</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>-35.69743251687063,174.5150518206609</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>-35.69813344607552,174.51530093523868</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>-35.69882820724929,174.51557522745432</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>-35.69950970910679,174.51589642847614</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>-35.70017988639615,174.5162537165797</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>-35.700846898132234,174.51662489541678</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>-35.70151820676015,174.5169811786421</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>-35.70218271870021,174.51733411956502</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>-35.702859627619674,174.5176420309661</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>-35.703546140338524,174.517946200564</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>-35.70420505103985,174.51832253859928</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>-35.70484950269469,174.51871021906618</t>
+        </is>
+      </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>-35.70549887174727,174.51908891393413</t>
+        </is>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>-35.70613925035653,174.51949413184983</t>
+        </is>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>-35.70678283461532,174.5199060950921</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>-35.70741415258758,174.52035686229456</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>-35.70804234492208,174.52081240926486</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>-35.70866869427839,174.52127138133645</t>
+        </is>
+      </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>-35.70927796377894,174.5217620359345</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>-35.70987027535229,174.5222626370593</t>
+        </is>
+      </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>-35.71047171118119,174.52275514327243</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>-35.71104524232971,174.52331006845336</t>
+        </is>
+      </c>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>-35.71158444075016,174.52391654285847</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>-35.71211573540594,174.52453127339191</t>
+        </is>
+      </c>
+      <c r="AD271" t="inlineStr">
+        <is>
+          <t>-35.71267956797173,174.5250981165962</t>
+        </is>
+      </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>-35.694539280622905,174.5147593517796</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>-35.69525614317214,174.5149481903502</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>-35.69598916133964,174.51480003099118</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>-35.696724923763085,174.51482992435243</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>-35.697434205199585,174.51504494232677</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>-35.698132952560975,174.51530294584495</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>-35.698828074266714,174.51557575540338</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>-35.699509881058574,174.51589579981626</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>-35.70018139098084,174.51624850798376</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>-35.700846115741804,174.51662760390604</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>-35.701519831737144,174.5169755532771</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>-35.70218278322527,174.5173339131783</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>-35.70286084240513,174.51763846116043</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>-35.70354887064146,174.5179382567873</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>-35.70420663950084,174.5183180828692</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>-35.70485049089409,174.51870773593004</t>
+        </is>
+      </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>-35.70549694759756,174.51909329215133</t>
+        </is>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>-35.706142579131644,174.51948717234046</t>
+        </is>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>-35.70678511400924,174.5199015859273</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>-35.707418948835134,174.52034737420487</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>-35.70804473182536,174.52080772170623</t>
+        </is>
+      </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>-35.708675857494896,174.52125745095535</t>
+        </is>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>-35.70929042424504,174.52173822113755</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>-35.709876623942996,174.52225176240478</t>
+        </is>
+      </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>-35.71046581239193,174.52276435992715</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>-35.71103516982135,174.52332580638753</t>
+        </is>
+      </c>
+      <c r="AB272" t="inlineStr">
+        <is>
+          <t>-35.71157279936002,174.52393456441467</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>-35.71211545223699,174.5245317033418</t>
+        </is>
+      </c>
+      <c r="AD272" t="inlineStr">
+        <is>
+          <t>-35.71267979589311,174.5250977740136</t>
+        </is>
+      </c>
+      <c r="AE272" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0097/nzd0097.xlsx
+++ b/data/nzd0097/nzd0097.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE272"/>
+  <dimension ref="A1:AE273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27352,6 +27352,105 @@
       <c r="AE272" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>394.5</v>
+      </c>
+      <c r="C273" t="n">
+        <v>402.47</v>
+      </c>
+      <c r="D273" t="n">
+        <v>382.33</v>
+      </c>
+      <c r="E273" t="n">
+        <v>361.46</v>
+      </c>
+      <c r="F273" t="n">
+        <v>359.35</v>
+      </c>
+      <c r="G273" t="n">
+        <v>360.18</v>
+      </c>
+      <c r="H273" t="n">
+        <v>362.87</v>
+      </c>
+      <c r="I273" t="n">
+        <v>367.88</v>
+      </c>
+      <c r="J273" t="n">
+        <v>373.52</v>
+      </c>
+      <c r="K273" t="n">
+        <v>381.71</v>
+      </c>
+      <c r="L273" t="n">
+        <v>386.7</v>
+      </c>
+      <c r="M273" t="n">
+        <v>393.24</v>
+      </c>
+      <c r="N273" t="n">
+        <v>391.25</v>
+      </c>
+      <c r="O273" t="n">
+        <v>387.99</v>
+      </c>
+      <c r="P273" t="n">
+        <v>392.61</v>
+      </c>
+      <c r="Q273" t="n">
+        <v>395.27</v>
+      </c>
+      <c r="R273" t="n">
+        <v>392.36</v>
+      </c>
+      <c r="S273" t="n">
+        <v>389.42</v>
+      </c>
+      <c r="T273" t="n">
+        <v>384.82</v>
+      </c>
+      <c r="U273" t="n">
+        <v>382.57</v>
+      </c>
+      <c r="V273" t="n">
+        <v>382.08</v>
+      </c>
+      <c r="W273" t="n">
+        <v>381.3</v>
+      </c>
+      <c r="X273" t="n">
+        <v>380.65</v>
+      </c>
+      <c r="Y273" t="n">
+        <v>384.47</v>
+      </c>
+      <c r="Z273" t="n">
+        <v>382.41</v>
+      </c>
+      <c r="AA273" t="n">
+        <v>382.96</v>
+      </c>
+      <c r="AB273" t="n">
+        <v>387.79</v>
+      </c>
+      <c r="AC273" t="n">
+        <v>394.65</v>
+      </c>
+      <c r="AD273" t="n">
+        <v>398.03</v>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -27366,7 +27465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B274"/>
+  <dimension ref="A1:B275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30109,6 +30208,16 @@
       </c>
       <c r="B274" t="n">
         <v>-0.12</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -30277,28 +30386,28 @@
         <v>0.0566</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09242281592422301</v>
+        <v>0.09379981266043994</v>
       </c>
       <c r="J2" t="n">
+        <v>272</v>
+      </c>
+      <c r="K2" t="n">
         <v>271</v>
       </c>
-      <c r="K2" t="n">
-        <v>270</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.01165576415674974</v>
+        <v>0.0120937149534347</v>
       </c>
       <c r="M2" t="n">
-        <v>4.391500764821195</v>
+        <v>4.381807360555191</v>
       </c>
       <c r="N2" t="n">
-        <v>38.23776768012307</v>
+        <v>38.10906823668865</v>
       </c>
       <c r="O2" t="n">
-        <v>6.183669434900533</v>
+        <v>6.173254266324096</v>
       </c>
       <c r="P2" t="n">
-        <v>390.1815960223092</v>
+        <v>390.1662905510377</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30359,28 +30468,28 @@
         <v>0.0609</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02307030915467282</v>
+        <v>-0.02141398544444127</v>
       </c>
       <c r="J3" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K3" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009240180259971753</v>
+        <v>0.0008021748903339621</v>
       </c>
       <c r="M3" t="n">
-        <v>4.368124393904278</v>
+        <v>4.360283285724553</v>
       </c>
       <c r="N3" t="n">
-        <v>30.32817151253147</v>
+        <v>30.23376547410342</v>
       </c>
       <c r="O3" t="n">
-        <v>5.507101915938316</v>
+        <v>5.498523935939846</v>
       </c>
       <c r="P3" t="n">
-        <v>400.8715735222938</v>
+        <v>400.8531199976707</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30437,28 +30546,28 @@
         <v>0.132</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.008640535467318614</v>
+        <v>-0.008847334245910584</v>
       </c>
       <c r="J4" t="n">
+        <v>272</v>
+      </c>
+      <c r="K4" t="n">
         <v>271</v>
       </c>
-      <c r="K4" t="n">
-        <v>270</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0002147200135456107</v>
+        <v>0.0002269402715611157</v>
       </c>
       <c r="M4" t="n">
-        <v>3.357646559764339</v>
+        <v>3.346315280501647</v>
       </c>
       <c r="N4" t="n">
-        <v>18.34955267915418</v>
+        <v>18.28212175901788</v>
       </c>
       <c r="O4" t="n">
-        <v>4.283637785709033</v>
+        <v>4.275759787338138</v>
       </c>
       <c r="P4" t="n">
-        <v>382.8358498678422</v>
+        <v>382.8381486360714</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30515,28 +30624,28 @@
         <v>0.1347</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0771029545521822</v>
+        <v>0.07306690851483706</v>
       </c>
       <c r="J5" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K5" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01485717901996941</v>
+        <v>0.01340178305355055</v>
       </c>
       <c r="M5" t="n">
-        <v>3.52004006927364</v>
+        <v>3.526825910297564</v>
       </c>
       <c r="N5" t="n">
-        <v>20.84186904285579</v>
+        <v>20.87185739215819</v>
       </c>
       <c r="O5" t="n">
-        <v>4.56528959025118</v>
+        <v>4.56857279597887</v>
       </c>
       <c r="P5" t="n">
-        <v>364.8089470886424</v>
+        <v>364.8537075026475</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30593,28 +30702,28 @@
         <v>0.114</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2127428033994812</v>
+        <v>0.2081254032169775</v>
       </c>
       <c r="J6" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K6" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08803266847502378</v>
+        <v>0.08476216320570562</v>
       </c>
       <c r="M6" t="n">
-        <v>3.87194668460109</v>
+        <v>3.883046675778692</v>
       </c>
       <c r="N6" t="n">
-        <v>24.79002427152783</v>
+        <v>24.83842245734965</v>
       </c>
       <c r="O6" t="n">
-        <v>4.978958151212744</v>
+        <v>4.983816053723256</v>
       </c>
       <c r="P6" t="n">
-        <v>359.8507852283261</v>
+        <v>359.9019929553647</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30671,28 +30780,28 @@
         <v>0.1066</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1717025652223086</v>
+        <v>0.1652740724257346</v>
       </c>
       <c r="J7" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K7" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06940643767764687</v>
+        <v>0.06434522292505462</v>
       </c>
       <c r="M7" t="n">
-        <v>3.604407865999162</v>
+        <v>3.624960259115056</v>
       </c>
       <c r="N7" t="n">
-        <v>20.89996880439502</v>
+        <v>21.09359858205609</v>
       </c>
       <c r="O7" t="n">
-        <v>4.571648368411007</v>
+        <v>4.592776783391077</v>
       </c>
       <c r="P7" t="n">
-        <v>364.2045693894314</v>
+        <v>364.27586243127</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30749,28 +30858,28 @@
         <v>0.1191</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05688274391350828</v>
+        <v>0.04967460354807857</v>
       </c>
       <c r="J8" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K8" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L8" t="n">
-        <v>0.007961155400789011</v>
+        <v>0.006035837341291983</v>
       </c>
       <c r="M8" t="n">
-        <v>3.582150944905517</v>
+        <v>3.60848599597159</v>
       </c>
       <c r="N8" t="n">
-        <v>21.31794971933374</v>
+        <v>21.57962576092645</v>
       </c>
       <c r="O8" t="n">
-        <v>4.617136528123654</v>
+        <v>4.645387579193629</v>
       </c>
       <c r="P8" t="n">
-        <v>371.0153852081907</v>
+        <v>371.0953246697276</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30827,28 +30936,28 @@
         <v>0.1247</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05739714145880477</v>
+        <v>0.05039403542287326</v>
       </c>
       <c r="J9" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K9" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0086751460150013</v>
+        <v>0.006647808722335058</v>
       </c>
       <c r="M9" t="n">
-        <v>3.408213760916499</v>
+        <v>3.434464657467335</v>
       </c>
       <c r="N9" t="n">
-        <v>19.90451090903004</v>
+        <v>20.15231317700295</v>
       </c>
       <c r="O9" t="n">
-        <v>4.461447176537008</v>
+        <v>4.489132786742107</v>
       </c>
       <c r="P9" t="n">
-        <v>375.7451775336135</v>
+        <v>375.8228431307323</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30905,28 +31014,28 @@
         <v>0.1072</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1227855026362206</v>
+        <v>0.117367821818911</v>
       </c>
       <c r="J10" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K10" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03078184903550929</v>
+        <v>0.02821206141493349</v>
       </c>
       <c r="M10" t="n">
-        <v>3.750143485257374</v>
+        <v>3.763010052109825</v>
       </c>
       <c r="N10" t="n">
-        <v>25.09879094345066</v>
+        <v>25.19861459146508</v>
       </c>
       <c r="O10" t="n">
-        <v>5.009869353930365</v>
+        <v>5.019822167314802</v>
       </c>
       <c r="P10" t="n">
-        <v>377.5007972504483</v>
+        <v>377.5608802212782</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30983,28 +31092,28 @@
         <v>0.1173</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1156303541337854</v>
+        <v>0.1143111836322312</v>
       </c>
       <c r="J11" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K11" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0352045064137958</v>
+        <v>0.03468327503953583</v>
       </c>
       <c r="M11" t="n">
-        <v>3.528485143074616</v>
+        <v>3.52115131329157</v>
       </c>
       <c r="N11" t="n">
-        <v>19.37369684146147</v>
+        <v>19.31385937340081</v>
       </c>
       <c r="O11" t="n">
-        <v>4.401556184062799</v>
+        <v>4.394753619191958</v>
       </c>
       <c r="P11" t="n">
-        <v>380.3830651644311</v>
+        <v>380.3976949821404</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31061,28 +31170,28 @@
         <v>0.1139</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07659525377861076</v>
+        <v>0.07758684587022931</v>
       </c>
       <c r="J12" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K12" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01474697507345479</v>
+        <v>0.01524164040227949</v>
       </c>
       <c r="M12" t="n">
-        <v>3.509881532287456</v>
+        <v>3.50152979723195</v>
       </c>
       <c r="N12" t="n">
-        <v>20.72432198666628</v>
+        <v>20.65456484809921</v>
       </c>
       <c r="O12" t="n">
-        <v>4.552397388922267</v>
+        <v>4.544729348167964</v>
       </c>
       <c r="P12" t="n">
-        <v>383.3211580483398</v>
+        <v>383.3101611290444</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31139,28 +31248,28 @@
         <v>0.1126</v>
       </c>
       <c r="I13" t="n">
-        <v>0.07774456131508659</v>
+        <v>0.08060397951431517</v>
       </c>
       <c r="J13" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K13" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0192126665904101</v>
+        <v>0.02071930517332576</v>
       </c>
       <c r="M13" t="n">
-        <v>3.239979758182481</v>
+        <v>3.241970227275542</v>
       </c>
       <c r="N13" t="n">
-        <v>16.31394592371568</v>
+        <v>16.30748037530267</v>
       </c>
       <c r="O13" t="n">
-        <v>4.039052602246681</v>
+        <v>4.03825214360157</v>
       </c>
       <c r="P13" t="n">
-        <v>387.3212235493842</v>
+        <v>387.2895121315195</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31217,28 +31326,28 @@
         <v>0.1163</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1490314878579754</v>
+        <v>0.1507641580368632</v>
       </c>
       <c r="J14" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K14" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0538818322732707</v>
+        <v>0.05544458265082997</v>
       </c>
       <c r="M14" t="n">
-        <v>3.577463578743078</v>
+        <v>3.572045141830831</v>
       </c>
       <c r="N14" t="n">
-        <v>20.62010547635858</v>
+        <v>20.56394475615564</v>
       </c>
       <c r="O14" t="n">
-        <v>4.540936629854967</v>
+        <v>4.534748587976585</v>
       </c>
       <c r="P14" t="n">
-        <v>384.9295842890123</v>
+        <v>384.9103686919096</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31295,28 +31404,28 @@
         <v>0.1195</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1948776102743014</v>
+        <v>0.1952101986788828</v>
       </c>
       <c r="J15" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K15" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L15" t="n">
-        <v>0.07219116015500382</v>
+        <v>0.07296276813820834</v>
       </c>
       <c r="M15" t="n">
-        <v>3.626053106630351</v>
+        <v>3.614129290202358</v>
       </c>
       <c r="N15" t="n">
-        <v>25.80656236837351</v>
+        <v>25.71240925590742</v>
       </c>
       <c r="O15" t="n">
-        <v>5.080015981113988</v>
+        <v>5.070740503704308</v>
       </c>
       <c r="P15" t="n">
-        <v>382.325917785415</v>
+        <v>382.3222293253368</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31373,28 +31482,28 @@
         <v>0.1336</v>
       </c>
       <c r="I16" t="n">
-        <v>0.150026213368536</v>
+        <v>0.1533871765813606</v>
       </c>
       <c r="J16" t="n">
+        <v>272</v>
+      </c>
+      <c r="K16" t="n">
         <v>271</v>
       </c>
-      <c r="K16" t="n">
-        <v>270</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.06807572681786422</v>
+        <v>0.07117410334807506</v>
       </c>
       <c r="M16" t="n">
-        <v>3.280799178530793</v>
+        <v>3.287367202759771</v>
       </c>
       <c r="N16" t="n">
-        <v>16.26631909733311</v>
+        <v>16.28016438931214</v>
       </c>
       <c r="O16" t="n">
-        <v>4.033152501125281</v>
+        <v>4.034868571504175</v>
       </c>
       <c r="P16" t="n">
-        <v>384.0868720409023</v>
+        <v>384.0495145624524</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31451,28 +31560,28 @@
         <v>0.1213</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1208354825083822</v>
+        <v>0.1262082057275946</v>
       </c>
       <c r="J17" t="n">
+        <v>272</v>
+      </c>
+      <c r="K17" t="n">
         <v>271</v>
       </c>
-      <c r="K17" t="n">
-        <v>270</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.04384486745454719</v>
+        <v>0.04749876746332171</v>
       </c>
       <c r="M17" t="n">
-        <v>3.361556027016986</v>
+        <v>3.376587075438162</v>
       </c>
       <c r="N17" t="n">
-        <v>16.80770879803525</v>
+        <v>16.93441733930888</v>
       </c>
       <c r="O17" t="n">
-        <v>4.099720575604543</v>
+        <v>4.115144874644011</v>
       </c>
       <c r="P17" t="n">
-        <v>384.8380678073815</v>
+        <v>384.7783447977723</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31529,28 +31638,28 @@
         <v>0.1036</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1514554146880447</v>
+        <v>0.1559585309438711</v>
       </c>
       <c r="J18" t="n">
+        <v>272</v>
+      </c>
+      <c r="K18" t="n">
         <v>271</v>
       </c>
-      <c r="K18" t="n">
-        <v>270</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.07647744686305502</v>
+        <v>0.08064724247416832</v>
       </c>
       <c r="M18" t="n">
-        <v>3.005332073521294</v>
+        <v>3.015979456452339</v>
       </c>
       <c r="N18" t="n">
-        <v>14.62155924809592</v>
+        <v>14.70018497267535</v>
       </c>
       <c r="O18" t="n">
-        <v>3.823814750755575</v>
+        <v>3.834082024771424</v>
       </c>
       <c r="P18" t="n">
-        <v>382.2684640989793</v>
+        <v>382.2184076109666</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -31607,28 +31716,28 @@
         <v>0.1031</v>
       </c>
       <c r="I19" t="n">
-        <v>0.194638107533169</v>
+        <v>0.1971179368501108</v>
       </c>
       <c r="J19" t="n">
+        <v>272</v>
+      </c>
+      <c r="K19" t="n">
         <v>271</v>
       </c>
-      <c r="K19" t="n">
-        <v>270</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.1080430279917212</v>
+        <v>0.1110625629067049</v>
       </c>
       <c r="M19" t="n">
-        <v>3.154388839940935</v>
+        <v>3.156800943942394</v>
       </c>
       <c r="N19" t="n">
-        <v>16.50869936394008</v>
+        <v>16.48798800692341</v>
       </c>
       <c r="O19" t="n">
-        <v>4.063089878890212</v>
+        <v>4.060540358982214</v>
       </c>
       <c r="P19" t="n">
-        <v>380.8883181111061</v>
+        <v>380.8607524122822</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31685,28 +31794,28 @@
         <v>0.1098</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1822441533453132</v>
+        <v>0.1839300686800049</v>
       </c>
       <c r="J20" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K20" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L20" t="n">
-        <v>0.09972825676130148</v>
+        <v>0.102024792490668</v>
       </c>
       <c r="M20" t="n">
-        <v>3.112481270086053</v>
+        <v>3.10868769276549</v>
       </c>
       <c r="N20" t="n">
-        <v>15.85237662603435</v>
+        <v>15.8126982273149</v>
       </c>
       <c r="O20" t="n">
-        <v>3.981504316967941</v>
+        <v>3.976518354957626</v>
       </c>
       <c r="P20" t="n">
-        <v>377.6742694759219</v>
+        <v>377.655572397727</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31763,28 +31872,28 @@
         <v>0.0916</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1282840763560777</v>
+        <v>0.1293497927309739</v>
       </c>
       <c r="J21" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K21" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L21" t="n">
-        <v>0.05265394669876755</v>
+        <v>0.05387174734098055</v>
       </c>
       <c r="M21" t="n">
-        <v>3.227646118036031</v>
+        <v>3.221404957066924</v>
       </c>
       <c r="N21" t="n">
-        <v>15.65506969825101</v>
+        <v>15.60494757817362</v>
       </c>
       <c r="O21" t="n">
-        <v>3.956648796424951</v>
+        <v>3.950309807872494</v>
       </c>
       <c r="P21" t="n">
-        <v>377.6995798546254</v>
+        <v>377.6877608848439</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -31841,28 +31950,28 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1623501649458715</v>
+        <v>0.1630783166756894</v>
       </c>
       <c r="J22" t="n">
+        <v>272</v>
+      </c>
+      <c r="K22" t="n">
         <v>271</v>
       </c>
-      <c r="K22" t="n">
-        <v>270</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.06781428516184085</v>
+        <v>0.06888974123105562</v>
       </c>
       <c r="M22" t="n">
-        <v>3.493161616684661</v>
+        <v>3.48458955251594</v>
       </c>
       <c r="N22" t="n">
-        <v>18.94786093652776</v>
+        <v>18.88135878644748</v>
       </c>
       <c r="O22" t="n">
-        <v>4.352914074103434</v>
+        <v>4.345268551706267</v>
       </c>
       <c r="P22" t="n">
-        <v>376.7607293830956</v>
+        <v>376.7525938659549</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -31919,28 +32028,28 @@
         <v>0.09669999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2628741685936692</v>
+        <v>0.2623142243381797</v>
       </c>
       <c r="J23" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K23" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1420157004207366</v>
+        <v>0.1424771371560316</v>
       </c>
       <c r="M23" t="n">
-        <v>3.764304033518073</v>
+        <v>3.752904492594625</v>
       </c>
       <c r="N23" t="n">
-        <v>21.60212435419843</v>
+        <v>21.5238129984218</v>
       </c>
       <c r="O23" t="n">
-        <v>4.647808553952974</v>
+        <v>4.639376358781619</v>
       </c>
       <c r="P23" t="n">
-        <v>374.9913347508927</v>
+        <v>374.9976453934837</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -31997,28 +32106,28 @@
         <v>0.0977</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3045345392042351</v>
+        <v>0.3026750735574187</v>
       </c>
       <c r="J24" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K24" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2279436346321609</v>
+        <v>0.2269910797385745</v>
       </c>
       <c r="M24" t="n">
-        <v>3.218206666574432</v>
+        <v>3.214450841105736</v>
       </c>
       <c r="N24" t="n">
-        <v>16.18696241443465</v>
+        <v>16.14880335755313</v>
       </c>
       <c r="O24" t="n">
-        <v>4.023302426419701</v>
+        <v>4.018557372684024</v>
       </c>
       <c r="P24" t="n">
-        <v>374.9363055814188</v>
+        <v>374.9572746185989</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -32075,28 +32184,28 @@
         <v>0.0916</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3166561671079137</v>
+        <v>0.3172949854617784</v>
       </c>
       <c r="J25" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K25" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1662313818597984</v>
+        <v>0.1679166151115408</v>
       </c>
       <c r="M25" t="n">
-        <v>4.061054931192636</v>
+        <v>4.049241932257506</v>
       </c>
       <c r="N25" t="n">
-        <v>25.91666640577956</v>
+        <v>25.82325085693503</v>
       </c>
       <c r="O25" t="n">
-        <v>5.090841424143906</v>
+        <v>5.081658278252783</v>
       </c>
       <c r="P25" t="n">
-        <v>375.150622992793</v>
+        <v>375.143419092126</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -32153,28 +32262,28 @@
         <v>0.1013</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1904423301573406</v>
+        <v>0.1935931509796643</v>
       </c>
       <c r="J26" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K26" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L26" t="n">
-        <v>0.07346936424560235</v>
+        <v>0.07612205252697435</v>
       </c>
       <c r="M26" t="n">
-        <v>3.76289742780847</v>
+        <v>3.765033520069148</v>
       </c>
       <c r="N26" t="n">
-        <v>23.56954414288072</v>
+        <v>23.54482171033568</v>
       </c>
       <c r="O26" t="n">
-        <v>4.854847489147391</v>
+        <v>4.852300661576494</v>
       </c>
       <c r="P26" t="n">
-        <v>373.1737981354222</v>
+        <v>373.1382665949045</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -32231,28 +32340,28 @@
         <v>0.1481</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2699246775004416</v>
+        <v>0.2725303562752561</v>
       </c>
       <c r="J27" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K27" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1016091761470018</v>
+        <v>0.1040166095897158</v>
       </c>
       <c r="M27" t="n">
-        <v>4.50258477103045</v>
+        <v>4.496963326430643</v>
       </c>
       <c r="N27" t="n">
-        <v>33.19619195453138</v>
+        <v>33.1160363769735</v>
       </c>
       <c r="O27" t="n">
-        <v>5.761613658909401</v>
+        <v>5.754653454116373</v>
       </c>
       <c r="P27" t="n">
-        <v>372.3057940126822</v>
+        <v>372.27640999303</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -32309,28 +32418,28 @@
         <v>0.0771</v>
       </c>
       <c r="I28" t="n">
-        <v>0.275033525731823</v>
+        <v>0.277481915928186</v>
       </c>
       <c r="J28" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K28" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L28" t="n">
-        <v>0.08219107353952282</v>
+        <v>0.08410119102074509</v>
       </c>
       <c r="M28" t="n">
-        <v>5.316772936871457</v>
+        <v>5.308314488295054</v>
       </c>
       <c r="N28" t="n">
-        <v>43.19553485857833</v>
+        <v>43.07235275374813</v>
       </c>
       <c r="O28" t="n">
-        <v>6.572331006467822</v>
+        <v>6.562953051313725</v>
       </c>
       <c r="P28" t="n">
-        <v>377.2334226640102</v>
+        <v>377.2056592911483</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -32387,28 +32496,28 @@
         <v>0.123</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2753546747735345</v>
+        <v>0.2741962825216394</v>
       </c>
       <c r="J29" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K29" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1077506932751952</v>
+        <v>0.1077033248608199</v>
       </c>
       <c r="M29" t="n">
-        <v>4.534284727156464</v>
+        <v>4.523428913439862</v>
       </c>
       <c r="N29" t="n">
-        <v>32.10635573958326</v>
+        <v>31.99537223604035</v>
       </c>
       <c r="O29" t="n">
-        <v>5.666247059525666</v>
+        <v>5.656445194292997</v>
       </c>
       <c r="P29" t="n">
-        <v>388.7807523695428</v>
+        <v>388.7938878885697</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -32469,28 +32578,28 @@
         <v>0.1952</v>
       </c>
       <c r="I30" t="n">
-        <v>0.01458570370277839</v>
+        <v>0.01478414156644309</v>
       </c>
       <c r="J30" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K30" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0002271442153989334</v>
+        <v>0.0002353157478451884</v>
       </c>
       <c r="M30" t="n">
-        <v>5.147998264609827</v>
+        <v>5.129690898154394</v>
       </c>
       <c r="N30" t="n">
-        <v>46.42063745185784</v>
+        <v>46.24701183427108</v>
       </c>
       <c r="O30" t="n">
-        <v>6.813269219094299</v>
+        <v>6.800515556505336</v>
       </c>
       <c r="P30" t="n">
-        <v>397.3890083345248</v>
+        <v>397.3867156798332</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -32532,7 +32641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE272"/>
+  <dimension ref="A1:AE273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75115,6 +75224,163 @@
         </is>
       </c>
     </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>-35.694539270589296,174.5147594615964</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>-35.69525705624421,174.51493819692948</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>-35.69598834209729,174.51480512672637</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>-35.69672811743837,174.5148165622931</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>-35.69743423117388,174.5150448365062</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>-35.69813264086755,174.51530421570152</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>-35.698826185913845,174.51558325227967</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>-35.69950910727548,174.51589862878578</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>-35.700181300705744,174.5162488204995</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>-35.700846597212866,174.5166259371434</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>-35.70152151689821,174.51696971956497</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>-35.70218507386476,174.51732658644949</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>-35.70286115477852,174.51763754321038</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>-35.70354659538905,174.51794487660123</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>-35.70420198242157,174.51833114625913</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>-35.70484788204756,174.5187142914093</t>
+        </is>
+      </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>-35.705499000023906,174.519088622053</t>
+        </is>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>-35.70614485911436,174.51948240555288</t>
+        </is>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>-35.706785161496605,174.51990149198636</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>-35.70741942371108,174.52034643478996</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>-35.708044827301485,174.5208075342039</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>-35.70866898273008,174.52127082038152</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>-35.709291203024,174.52173673271247</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>-35.70987877511815,174.52224807760413</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>-35.71046113787923,174.52277166369035</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>-35.711036060208905,174.5233244151891</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>-35.71158634366946,174.52391359702665</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>-35.712119699770966,174.52452525409325</t>
+        </is>
+      </c>
+      <c r="AD273" t="inlineStr">
+        <is>
+          <t>-35.71266874170491,174.5251143892692</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
